--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10.08.2026 à 09:42</t>
+          <t>12.08.2026 à 22:18</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="K4" s="11" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="K7" s="11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -1857,13 +1857,17 @@
           <t>https://www.acea.auto</t>
         </is>
       </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
+      <c r="O9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>2025-11 → 2025-11</t>
+        </is>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -1994,7 +1998,7 @@
         </is>
       </c>
       <c r="K11" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -2012,7 +2016,7 @@
         </is>
       </c>
       <c r="O11" s="11" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
@@ -2020,7 +2024,7 @@
         </is>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -2075,7 +2079,7 @@
         </is>
       </c>
       <c r="K12" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
@@ -2093,7 +2097,7 @@
         </is>
       </c>
       <c r="O12" s="11" t="n">
-        <v>656</v>
+        <v>697</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
@@ -2101,7 +2105,7 @@
         </is>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -2156,7 +2160,7 @@
         </is>
       </c>
       <c r="K13" s="11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
@@ -2174,15 +2178,15 @@
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>99</v>
+        <v>550</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>2024-01 → 2024-03</t>
+          <t>2023-01 → 2026-05</t>
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -2314,7 +2318,7 @@
         </is>
       </c>
       <c r="K15" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
@@ -2332,7 +2336,7 @@
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
@@ -2340,7 +2344,7 @@
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -2547,7 +2551,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
@@ -2565,7 +2569,7 @@
         </is>
       </c>
       <c r="O18" s="11" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
@@ -2573,7 +2577,7 @@
         </is>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -2628,7 +2632,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -2646,7 +2650,7 @@
         </is>
       </c>
       <c r="O19" s="11" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
         </is>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -3015,7 +3019,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
@@ -3033,7 +3037,7 @@
         </is>
       </c>
       <c r="O24" s="11" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
@@ -3041,7 +3045,7 @@
         </is>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -3096,7 +3100,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
@@ -3114,7 +3118,7 @@
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>1032</v>
+        <v>1118</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
@@ -3122,7 +3126,7 @@
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -3270,7 +3274,7 @@
         </is>
       </c>
       <c r="O27" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
@@ -3278,7 +3282,7 @@
         </is>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilan'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bilan'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Indicateurs'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instanciation QV'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Instanciation QV'!$1:$1</definedName>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Couverture QV'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lacunes'!$A$1:$H$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lacunes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Sources'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12.08.2026 à 22:18</t>
+          <t>23.08.2026 à 21:02</t>
         </is>
       </c>
     </row>
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>0</v>
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0</v>
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTA(Indicateurs!$J$2:$J$27)</f>
+        <f>COUNTA(Indicateurs!$J$2:$J$33)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$27,"certifie")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$33,"certifie")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$27,"certifie",Indicateurs!$G$2:$G$27,"hard")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$33,"certifie",Indicateurs!$G$2:$G$33,"hard")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$27,"certifie",Indicateurs!$G$2:$G$27,"composite")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$33,"certifie",Indicateurs!$G$2:$G$33,"composite")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$27,"a_confirmer")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$33,"a_confirmer")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1147,7 +1147,7 @@
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -1467,15 +1467,15 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>378</v>
+        <v>903</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2014 → 2025</t>
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>mia USD</t>
+          <t>mio USD</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
@@ -1547,13 +1547,17 @@
           <t>https://milex.sipri.org</t>
         </is>
       </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="11" t="n"/>
+      <c r="O5" s="11" t="n">
+        <v>429</v>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>2014 → 2025</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1700,46 +1704,46 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>102</v>
+        <v>438</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Aérospatial</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Production mondiale de véhicules par pays</t>
+          <t>Avis de marchés publics UE en aéronefs et engins spatiaux (TED, CPV 347)</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>QV1, QV3</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>OICA</t>
+          <t>Office des publications de l'UE</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -1749,12 +1753,12 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>unités</t>
+          <t>nombre d'avis</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -1762,9 +1766,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K8" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="K8" s="11" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -1772,26 +1774,30 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="n"/>
-      <c r="Q8" s="11" t="n"/>
+          <t>https://ted.europa.eu</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>2025-09 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -1801,32 +1807,32 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Immatriculations de véhicules neufs en Europe</t>
+          <t>Production mondiale de véhicules par pays</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1, QV3</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Immatriculations de véhicules neufs</t>
+          <t>Statistiques de production automobile</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>ACEA</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -1849,30 +1855,26 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>Tableaux web</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>https://www.acea.auto</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>2025-11 → 2025-11</t>
-        </is>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>30</v>
-      </c>
+          <t>https://www.oica.net/production-statistics</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -1882,32 +1884,32 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Ventes mondiales de véhicules électriques par pays</t>
+          <t>Immatriculations de véhicules neufs en Europe</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3, QV4</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Global EV Data Explorer</t>
+          <t>Immatriculations de véhicules neufs</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Agence internationale de l'énergie</t>
+          <t>ACEA</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1921,7 +1923,7 @@
         </is>
       </c>
       <c r="K10" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
@@ -1930,26 +1932,30 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>https://www.iea.org</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="n"/>
-      <c r="Q10" s="11" t="n"/>
+          <t>https://www.acea.auto</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>2025-11 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -1959,22 +1965,22 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de parties et accessoires automobiles (SH 8708)</t>
+          <t>Ventes mondiales de véhicules électriques par pays</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV2, QV3, QV4</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Global EV Data Explorer</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Agence internationale de l'énergie</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1989,7 +1995,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>unités</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
@@ -2002,21 +2008,21 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.iea.org</t>
         </is>
       </c>
       <c r="O11" s="11" t="n">
-        <v>94</v>
+        <v>3239</v>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
@@ -2024,13 +2030,13 @@
         </is>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -2040,22 +2046,22 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Production industrielle automobile UE (NACE C29)</t>
+          <t>Commerce mondial de parties et accessoires automobiles (SH 8708)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -2065,12 +2071,12 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -2083,7 +2089,7 @@
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -2093,50 +2099,50 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O12" s="11" t="n">
-        <v>697</v>
+        <v>503</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Exportations horlogères suisses par marché de destination</t>
+          <t>Production industrielle automobile UE (NACE C29)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -2151,7 +2157,7 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -2160,11 +2166,11 @@
         </is>
       </c>
       <c r="K13" s="11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -2174,25 +2180,25 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>550</v>
+        <v>1411</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2023-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -2202,22 +2208,22 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
+          <t>Exportations horlogères suisses par marché de destination</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -2227,12 +2233,12 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -2241,35 +2247,39 @@
         </is>
       </c>
       <c r="K14" s="11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="11" t="n"/>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>23473</v>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-05</t>
+        </is>
+      </c>
+      <c r="Q14" s="11" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -2279,22 +2289,22 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
+          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -2309,7 +2319,7 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
@@ -2318,39 +2328,39 @@
         </is>
       </c>
       <c r="K15" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV / Excel</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bfs.admin.ch</t>
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2023 → 2023</t>
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -2360,22 +2370,22 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
+          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -2390,7 +2400,7 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -2403,187 +2413,187 @@
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
+          <t>libre_quota</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>534</v>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>2015 → 2025</t>
+        </is>
+      </c>
+      <c r="Q16" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>QV4</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Statistiques de propriété intellectuelle</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>OMPI</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>https://www.wipo.int/ipstats</t>
         </is>
       </c>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P16" s="11" t="n"/>
-      <c r="Q16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Climat de branche et perspectives</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>QV1, QV5</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Swiss Watch Industry Study</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>composite</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>qualitatif</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="N17" s="13" t="inlineStr">
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t>https://www.deloitte.com/ch</t>
         </is>
       </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="13" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>QV2, QV3</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>UN Comtrade — commerce international par code SH</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Nations Unies</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>libre_quota</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>https://comtradeplus.un.org</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>117</v>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>2023 → 2025</t>
-        </is>
-      </c>
-      <c r="Q18" s="11" t="n">
-        <v>25</v>
-      </c>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -2593,22 +2603,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
+          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2618,12 +2628,12 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -2636,7 +2646,7 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -2646,25 +2656,25 @@
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O19" s="11" t="n">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -2674,22 +2684,22 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -2699,12 +2709,12 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>pourcentage / USD</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -2713,7 +2723,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
@@ -2722,280 +2732,292 @@
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="11" t="n"/>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>796</v>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q20" s="11" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Médical</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>QV2, QV5</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Global Health Expenditure Database</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>OMS</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage du PIB</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>2871</v>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2023</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Office fédéral de la statistique</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K22" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>CSV / Excel</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>https://www.bfs.admin.ch</t>
         </is>
       </c>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="O22" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2023</t>
+        </is>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Médical</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Panorama de la branche medtech suisse</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>QV1, QV3</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medical Technology Industry report</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medtech</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>bisannuelle</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>mia CHF</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.swiss-medtech.ch</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Panorama de la branche medtech suisse</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>QV1, QV3</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medical Technology Industry report</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medtech</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>composite</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>bisannuelle</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>mia CHF</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M22" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N22" s="13" t="inlineStr">
-        <is>
-          <t>https://www.swiss-medtech.ch</t>
-        </is>
-      </c>
-      <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Dépôts de brevets en technologies médicales</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>QV4</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Statistiques de propriété intellectuelle</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>OMPI</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="11" t="n"/>
+      <c r="P23" s="13" t="n"/>
+      <c r="Q23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Indicateur composite avancé (CLI), zone G20</t>
+          <t>Dépôts de brevets en technologies médicales</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -3005,12 +3027,12 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -3019,7 +3041,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
@@ -3028,55 +3050,51 @@
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
-        </is>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>2023-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q24" s="11" t="n">
-        <v>25</v>
-      </c>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Taux de change CHF/USD et CHF/EUR</t>
+          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>Office des publications de l'UE</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -3091,7 +3109,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>taux</t>
+          <t>nombre d'avis</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -3099,9 +3117,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K25" s="11" t="n">
-        <v>7</v>
-      </c>
+      <c r="K25" s="11" t="n"/>
       <c r="L25" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3109,55 +3125,55 @@
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://ted.europa.eu</t>
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>1118</v>
+        <v>14</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2026-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de marchandises (volume)</t>
+          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV4</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>World Trade Monitor</t>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+          <t>U.S. Food and Drug Administration</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -3172,7 +3188,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre d'autorisations</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -3180,9 +3196,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K26" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="K26" s="11" t="n"/>
       <c r="L26" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3190,103 +3204,587 @@
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor</t>
-        </is>
-      </c>
-      <c r="O26" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P26" s="11" t="n"/>
-      <c r="Q26" s="11" t="n"/>
+          <t>https://open.fda.gov</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>2025-09 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q26" s="11" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Indicateur composite avancé (CLI), zone G20</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Principaux indicateurs économiques et CLI</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>OCDE</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>https://data-explorer.oecd.org</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>798</v>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Taux de change CHF/USD et CHF/EUR</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Taux de change de référence</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Banque nationale suisse</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>https://data.snb.ch</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>2580</v>
+      </c>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q28" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Commerce mondial de marchandises (volume)</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>World Trade Monitor</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>https://www.cpb.nl/en/worldtrademonitor</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>164</v>
+      </c>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-05</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Croissance du PIB mondial</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>QV0</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>World Economic Outlook</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Fonds monétaire international</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>semestrielle</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>pourcentage</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M30" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="N30" s="11" t="inlineStr">
         <is>
           <t>https://www.imf.org/en/Publications/WEO</t>
         </is>
       </c>
-      <c r="O27" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="O30" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
         <is>
           <t>2023 → 2025</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="n">
-        <v>25</v>
+      <c r="Q30" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>solde d'opinion</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="n">
+        <v>274</v>
+      </c>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Baromètre conjoncturel KOF (Suisse)</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Baromètre conjoncturel KOF</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>KOF ETH Zurich</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>https://data.kof.ethz.ch</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="n">
+        <v>301</v>
+      </c>
+      <c r="P32" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q32" s="11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="P33" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="n">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q27"/>
+  <autoFilter ref="A1:Q33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3423,10 +3921,10 @@
         </is>
       </c>
       <c r="G3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="16" t="n">
         <v>3</v>
-      </c>
-      <c r="H3" s="16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3537,10 +4035,10 @@
         </is>
       </c>
       <c r="G6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="15" t="n">
         <v>2</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3993,10 +4491,10 @@
         </is>
       </c>
       <c r="G18" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -4069,10 +4567,10 @@
         </is>
       </c>
       <c r="G20" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4107,10 +4605,10 @@
         </is>
       </c>
       <c r="G21" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4145,10 +4643,10 @@
         </is>
       </c>
       <c r="G22" s="15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4223,7 +4721,7 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -4273,7 +4771,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -4323,7 +4821,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4348,7 +4846,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4436,10 +4934,10 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11" t="n">
         <v>3</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>2</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
@@ -4505,10 +5003,10 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
@@ -4781,10 +5279,10 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -4827,10 +5325,10 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -4850,10 +5348,10 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
@@ -4873,10 +5371,10 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
@@ -5079,7 +5577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5744,7 +6242,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>A5, M2</t>
+          <t>A5, M2, T5, T7</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
@@ -5939,17 +6437,17 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>ocde</t>
+          <t>kof</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>Baromètre conjoncturel KOF</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>KOF ETH Zurich</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -5959,7 +6457,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -5979,49 +6477,49 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
+          <t>https://data.kof.ethz.ch</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>Vérifié le 10.08.2026 : la série CLI est vivante et mensuelle, mais l'agrégat « OCDE total » n'est plus publié — 22 zones disponibles dont G20, G7, G4E, NAFTA. T1 réancré sur G20. Version du flux non épinglée : la 4.1 ne porte plus la mesure LI. Limitation de débit annoncée par la documentation sans être chiffrée.</t>
+          <t>API v2 publique sans clé (access_type=public), CSV date/valeur, mensuel depuis 1991. Vérifiée en réponse réelle le 17.08.2026. Ancienne API v1 hors service — motif du re-sourçage documenté.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>ofs</t>
+          <t>ocde</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -6046,34 +6544,34 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>H2, M4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>Nomenclature NOGA</t>
+          <t>Vérifié le 10.08.2026 : la série CLI est vivante et mensuelle, mais l'agrégat « OCDE total » n'est plus publié — 22 zones disponibles dont G20, G7, G4E, NAFTA. T1 réancré sur G20. Version du flux non épinglée : la 4.1 ne porte plus la mesure LI. Limitation de débit annoncée par la documentation sans être chiffrée.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>oica</t>
+          <t>ofs</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>OICA</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -6083,7 +6581,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>CSV / Excel</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -6108,30 +6606,34 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H2, M4</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="n"/>
+          <t>https://www.bfs.admin.ch</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>Nomenclature NOGA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>ompi</t>
+          <t>oica</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>Statistiques de production automobile</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -6141,7 +6643,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>Tableaux web</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -6166,34 +6668,30 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>H4, M6</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>Classification CIB</t>
-        </is>
-      </c>
+          <t>https://www.oica.net/production-statistics</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>oms_ghed</t>
+          <t>ompi</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -6203,7 +6701,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -6228,254 +6726,440 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>H4, M6</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="n"/>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>Classification CIB</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>oms_ghed</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Global Health Expenditure Database</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>OMS</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>openfda</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>U.S. Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>https://open.fda.gov</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>sipri</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Military Expenditure Database</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>SIPRI</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>https://milex.sipri.org</t>
         </is>
       </c>
-      <c r="L20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="L22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>sp_global_pmi</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Indices PMI manufacturiers</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>S&amp;P Global</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Communiqués</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>payant</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>https://www.pmi.spglobal.com</t>
         </is>
       </c>
-      <c r="L21" s="13" t="inlineStr">
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>Indices détaillés payants ; valeurs de synthèse dans les communiqués</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>swiss_medtech</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Swiss Medical Technology Industry report</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Swiss Medtech</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>bisannuelle</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>https://www.swiss-medtech.ch</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>Publication bisannuelle, périodes non alignées sur la fenêtre 2023-2025</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ted</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Office des publications de l'UE</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>M7, S7</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>API de recherche v3, POST JSON, sans clé pour la recherche. Vérifiée en réponse réelle le 20.08.2026 (totalNoticeCount par requête CPV + bornes de dates). Source de la famille OSINT F3 (marchés publics) de la demande de ratification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>unoosa</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Objets lancés dans l'espace</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>UNOOSA / Our World in Data</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>https://ourworldindata.org/space-exploration-satellites</t>
         </is>
       </c>
-      <c r="L23" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:L26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilan'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bilan'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Indicateurs'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instanciation QV'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Instanciation QV'!$1:$1</definedName>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23.08.2026 à 21:02</t>
+          <t>24.08.2026 à 14:10</t>
         </is>
       </c>
     </row>
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>1</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTA(Indicateurs!$J$2:$J$33)</f>
+        <f>COUNTA(Indicateurs!$J$2:$J$40)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$33,"certifie")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$40,"certifie")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$33,"certifie",Indicateurs!$G$2:$G$33,"hard")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$40,"certifie",Indicateurs!$G$2:$G$40,"hard")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$33,"certifie",Indicateurs!$G$2:$G$33,"composite")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$40,"certifie",Indicateurs!$G$2:$G$40,"composite")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$33,"a_confirmer")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$40,"a_confirmer")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1146,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>903</v>
+        <v>1089</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>https://milex.sipri.org</t>
+          <t>https://www.sipri.org/databases/milex</t>
         </is>
       </c>
       <c r="O5" s="11" t="n">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>438</v>
+        <v>570</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1797,32 +1797,32 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Aérospatial</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Production mondiale de véhicules par pays</t>
+          <t>Production aéronautique et spatiale UE (NACE C30.3)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>QV1, QV3</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>OICA</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>unités</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="K9" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
@@ -1855,26 +1855,30 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>192</v>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -1884,32 +1888,32 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Immatriculations de véhicules neufs en Europe</t>
+          <t>Production mondiale de véhicules par pays</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1, QV3</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Immatriculations de véhicules neufs</t>
+          <t>Statistiques de production automobile</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>ACEA</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1932,30 +1936,26 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>Tableaux web</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>https://www.acea.auto</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>2025-11 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q10" s="11" t="n">
-        <v>64</v>
-      </c>
+          <t>https://www.oica.net/production-statistics</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="n"/>
+      <c r="Q10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -1965,32 +1965,32 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Ventes mondiales de véhicules électriques par pays</t>
+          <t>Immatriculations de véhicules neufs en Europe</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3, QV4</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Global EV Data Explorer</t>
+          <t>Immatriculations de véhicules neufs</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Agence internationale de l'énergie</t>
+          <t>ACEA</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="K11" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -2013,30 +2013,30 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>https://www.iea.org</t>
+          <t>https://www.acea.auto</t>
         </is>
       </c>
       <c r="O11" s="11" t="n">
-        <v>3239</v>
+        <v>8</v>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2025-11 → 2026-06</t>
         </is>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de parties et accessoires automobiles (SH 8708)</t>
+          <t>Ventes mondiales de véhicules électriques par pays</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV2, QV3, QV4</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Global EV Data Explorer</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Agence internationale de l'énergie</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>unités</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -2089,35 +2089,35 @@
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.iea.org</t>
         </is>
       </c>
       <c r="O12" s="11" t="n">
-        <v>503</v>
+        <v>3513</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2023 → 2025</t>
         </is>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -2127,22 +2127,22 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Production industrielle automobile UE (NACE C29)</t>
+          <t>Commerce mondial de parties et accessoires automobiles (SH 8708)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -2180,50 +2180,50 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>1411</v>
+        <v>677</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-06</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Exportations horlogères suisses par marché de destination</t>
+          <t>Production industrielle automobile UE (NACE C29)</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -2247,11 +2247,11 @@
         </is>
       </c>
       <c r="K14" s="11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -2261,50 +2261,50 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O14" s="11" t="n">
-        <v>23473</v>
+        <v>1529</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
+          <t>Production d'équipements automobiles UE (NACE C29.3)</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV1, QV2</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="K15" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
@@ -2337,30 +2337,30 @@
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
+          <t>Exportations horlogères suisses par marché de destination</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="K16" s="11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
@@ -2427,21 +2427,21 @@
         </is>
       </c>
       <c r="O16" s="11" t="n">
-        <v>534</v>
+        <v>31815</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2023-01 → 2026-05</t>
         </is>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -2451,22 +2451,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
+          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -2490,135 +2490,145 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>CSV / Excel</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>https://www.bfs.admin.ch</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2023</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>QV2, QV3</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>UN Comtrade — commerce international par code SH</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Nations Unies</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Horlogerie</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Climat de branche et perspectives</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>QV1, QV5</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Watch Industry Study</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>composite</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>qualitatif</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N18" s="13" t="inlineStr">
-        <is>
-          <t>https://www.deloitte.com/ch</t>
-        </is>
-      </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>libre_quota</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>686</v>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>2015 → 2025</t>
+        </is>
+      </c>
+      <c r="Q18" s="11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
+          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2633,7 +2643,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -2642,145 +2652,135 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>549</v>
-      </c>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
-          <t>2015 → 2025</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="n">
-        <v>91</v>
-      </c>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>QV1</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Commission européenne</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Climat de branche et perspectives</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>QV1, QV5</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Watch Industry Study</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>qualitatif</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
-        </is>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>796</v>
-      </c>
-      <c r="P20" s="11" t="inlineStr">
-        <is>
-          <t>2023-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q20" s="11" t="n">
-        <v>91</v>
-      </c>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/ch</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>H6</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+          <t>Production horlogère UE (NACE C26.52)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>pourcentage du PIB</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -2813,30 +2813,30 @@
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O21" s="11" t="n">
-        <v>2871</v>
+        <v>192</v>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q21" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -2846,153 +2846,159 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
+          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
+          <t>QV2, QV3</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>UN Comtrade — commerce international par code SH</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Nations Unies</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>libre_quota</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>723</v>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>2015 → 2025</t>
+        </is>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Médical</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>STATENT et statistiques conjoncturelles</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Office fédéral de la statistique</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K22" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="K23" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>CSV / Excel</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>https://www.bfs.admin.ch</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="P22" s="11" t="inlineStr">
-        <is>
-          <t>2023 → 2023</t>
-        </is>
-      </c>
-      <c r="Q22" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Panorama de la branche medtech suisse</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>QV1, QV3</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medical Technology Industry report</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medtech</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>composite</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>bisannuelle</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>mia CHF</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N23" s="13" t="inlineStr">
-        <is>
-          <t>https://www.swiss-medtech.ch</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="13" t="n"/>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>976</v>
+      </c>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>2015-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -3002,22 +3008,22 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Dépôts de brevets en technologies médicales</t>
+          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -3032,7 +3038,7 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>pourcentage du PIB</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -3041,7 +3047,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
@@ -3050,26 +3056,30 @@
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="11" t="n"/>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>3281</v>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2023</t>
+        </is>
+      </c>
+      <c r="Q24" s="11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -3079,22 +3089,22 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
+          <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Office des publications de l'UE</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -3104,12 +3114,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>nombre d'avis</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -3117,7 +3127,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K25" s="11" t="n"/>
+      <c r="K25" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3125,134 +3137,130 @@
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>CSV / Excel</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu</t>
+          <t>https://www.bfs.admin.ch</t>
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>2026-01 → 2026-07</t>
+          <t>2023 → 2023</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>QV2, QV4</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>U.S. Food and Drug Administration</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>nombre d'autorisations</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="n"/>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Panorama de la branche medtech suisse</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>QV1, QV3</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medical Technology Industry report</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medtech</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>bisannuelle</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>mia CHF</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>https://open.fda.gov</t>
-        </is>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="P26" s="11" t="inlineStr">
-        <is>
-          <t>2025-09 → 2026-07</t>
-        </is>
-      </c>
-      <c r="Q26" s="11" t="n">
-        <v>80</v>
-      </c>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N26" s="13" t="inlineStr">
+        <is>
+          <t>https://www.swiss-medtech.ch</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Indicateur composite avancé (CLI), zone G20</t>
+          <t>Dépôts de brevets en technologies médicales</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -3262,12 +3270,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -3276,7 +3284,7 @@
         </is>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -3285,55 +3293,51 @@
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="n">
-        <v>798</v>
-      </c>
-      <c r="P27" s="11" t="inlineStr">
-        <is>
-          <t>2023-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q27" s="11" t="n">
-        <v>91</v>
-      </c>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Taux de change CHF/USD et CHF/EUR</t>
+          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>Office des publications de l'UE</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -3348,7 +3352,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>taux</t>
+          <t>nombre d'avis</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -3356,9 +3360,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K28" s="11" t="n">
-        <v>7</v>
-      </c>
+      <c r="K28" s="11" t="n"/>
       <c r="L28" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3366,55 +3368,55 @@
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://ted.europa.eu</t>
         </is>
       </c>
       <c r="O28" s="11" t="n">
-        <v>2580</v>
+        <v>14</v>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2026-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de marchandises (volume)</t>
+          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV4</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>World Trade Monitor</t>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+          <t>U.S. Food and Drug Administration</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -3429,7 +3431,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre d'autorisations</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
@@ -3437,9 +3439,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K29" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="K29" s="11" t="n"/>
       <c r="L29" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3447,30 +3447,30 @@
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor</t>
+          <t>https://open.fda.gov</t>
         </is>
       </c>
       <c r="O29" s="11" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2025-09 → 2026-07</t>
         </is>
       </c>
       <c r="Q29" s="11" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Croissance du PIB mondial</t>
+          <t>Indicateur composite avancé (CLI), zone G20</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>World Economic Outlook</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Fonds monétaire international</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>semestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -3518,7 +3518,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K30" s="11" t="n"/>
+      <c r="K30" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3526,30 +3528,30 @@
       </c>
       <c r="M30" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/Publications/WEO</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="O30" s="11" t="n">
-        <v>69</v>
+        <v>882</v>
       </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2023-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q30" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -3559,7 +3561,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -3584,12 +3586,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>trimestrielle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>solde d'opinion</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -3614,21 +3616,21 @@
         </is>
       </c>
       <c r="O31" s="11" t="n">
-        <v>274</v>
+        <v>51</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014-T1 → 2026-T3</t>
         </is>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -3638,7 +3640,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF (Suisse)</t>
+          <t>Production manufacturière suisse (NACE C)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -3648,12 +3650,12 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>KOF ETH Zurich</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -3676,7 +3678,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K32" s="11" t="n"/>
+      <c r="K32" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3684,107 +3688,664 @@
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>https://data.kof.ethz.ch</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O32" s="11" t="n">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Taux de change CHF/USD et CHF/EUR</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Taux de change de référence</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Banque nationale suisse</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>https://data.snb.ch</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>2752</v>
+      </c>
+      <c r="P33" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Commerce mondial de marchandises (volume)</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>World Trade Monitor</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+        </is>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>164</v>
+      </c>
+      <c r="P34" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-05</t>
+        </is>
+      </c>
+      <c r="Q34" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Croissance du PIB mondial</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>World Economic Outlook</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Fonds monétaire international</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>semestrielle</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.imf.org/en/Publications/WEO</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="P35" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2025</t>
+        </is>
+      </c>
+      <c r="Q35" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>solde d'opinion</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>468</v>
+      </c>
+      <c r="P36" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q36" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Baromètre conjoncturel KOF (Suisse)</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Baromètre conjoncturel KOF</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>KOF ETH Zurich</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>https://data.kof.ethz.ch</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>387</v>
+      </c>
+      <c r="P37" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q37" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>QV0</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Commission européenne</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>indice</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr">
+      <c r="M38" s="11" t="inlineStr">
         <is>
           <t>API + CSV</t>
         </is>
       </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="N38" s="11" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
-      <c r="O33" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="P33" s="11" t="inlineStr">
-        <is>
-          <t>2023-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q33" s="11" t="n">
-        <v>91</v>
+      <c r="O38" s="11" t="n">
+        <v>402</v>
+      </c>
+      <c r="P38" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q38" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>solde</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>194</v>
+      </c>
+      <c r="P39" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q39" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>trimestrielle</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="P40" s="11" t="inlineStr">
+        <is>
+          <t>2014-T1 → 2026-T3</t>
+        </is>
+      </c>
+      <c r="Q40" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q33"/>
+  <autoFilter ref="A1:Q40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3883,10 +4444,10 @@
         </is>
       </c>
       <c r="G2" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -4073,10 +4634,10 @@
         </is>
       </c>
       <c r="G7" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4111,10 +4672,10 @@
         </is>
       </c>
       <c r="G8" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4263,10 +4824,10 @@
         </is>
       </c>
       <c r="G12" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="15" t="n">
         <v>2</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4643,10 +5204,10 @@
         </is>
       </c>
       <c r="G22" s="15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4721,7 +5282,7 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -4746,7 +5307,7 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4771,7 +5332,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -4911,10 +5472,10 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -5026,10 +5587,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -5049,10 +5610,10 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -5141,10 +5702,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -5371,10 +5932,10 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
@@ -5589,7 +6150,7 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
@@ -6065,10 +6626,14 @@
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="n"/>
+          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>URL corrigée le 24.08.2026 : l'ancienne (…/en/worldtrademonitor) renvoyait 404. La nouvelle redirige vers le millésime courant.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -6242,7 +6807,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>A5, M2, T5, T7</t>
+          <t>A5, A6, H6, M2, S8, T10, T11, T5, T7, T8, T9</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
@@ -6913,10 +7478,14 @@
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>https://milex.sipri.org</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="n"/>
+          <t>https://www.sipri.org/databases/milex</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>URL corrigée le 24.08.2026 : l'ancienne (milex.sipri.org) échouait à la négociation TLS. Adresse alignée sur celle de la liaison S4.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilan'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bilan'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Indicateurs'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instanciation QV'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Instanciation QV'!$1:$1</definedName>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 14:10</t>
+          <t>24.08.2026 à 14:43</t>
         </is>
       </c>
     </row>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTA(Indicateurs!$J$2:$J$40)</f>
+        <f>COUNTA(Indicateurs!$J$2:$J$43)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$40,"certifie")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$43,"certifie")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$40,"certifie",Indicateurs!$G$2:$G$40,"hard")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$43,"certifie",Indicateurs!$G$2:$G$43,"hard")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$40,"certifie",Indicateurs!$G$2:$G$40,"composite")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$43,"certifie",Indicateurs!$G$2:$G$43,"composite")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$40,"a_confirmer")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$43,"a_confirmer")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2836,32 +2836,32 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
+          <t>Exportations horlogères suisses, valeur totale (FH)</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>mio CHF</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -2885,64 +2885,64 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O22" s="11" t="n">
-        <v>723</v>
+        <v>19</v>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>H8</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
+          <t>Exportations de montres mécaniques, valeur (FH)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV1, QV2</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>mio CHF</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
@@ -2975,55 +2975,55 @@
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O23" s="11" t="n">
-        <v>976</v>
+        <v>19</v>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>2015-01 → 2026-06</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>H9</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+          <t>Exportations de montres mécaniques, volume (FH)</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>pourcentage du PIB</t>
+          <t>milliers de pièces</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
@@ -3056,30 +3056,30 @@
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O24" s="11" t="n">
-        <v>3281</v>
+        <v>19</v>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -3089,22 +3089,22 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
+          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -3128,29 +3128,29 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>11</v>
+        <v>723</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n">
@@ -3158,84 +3158,90 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Panorama de la branche medtech suisse</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>QV1, QV3</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medical Technology Industry report</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medtech</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>composite</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>bisannuelle</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>mia CHF</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>QV1</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N26" s="13" t="inlineStr">
-        <is>
-          <t>https://www.swiss-medtech.ch</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>976</v>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>2015-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q26" s="11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -3245,22 +3251,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Dépôts de brevets en technologies médicales</t>
+          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -3275,7 +3281,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>pourcentage du PIB</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -3284,7 +3290,7 @@
         </is>
       </c>
       <c r="K27" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -3293,26 +3299,30 @@
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="O27" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="11" t="n"/>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>3281</v>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2023</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -3322,22 +3332,22 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
+          <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Office des publications de l'UE</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -3347,12 +3357,12 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>nombre d'avis</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -3360,7 +3370,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K28" s="11" t="n"/>
+      <c r="K28" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3368,134 +3380,130 @@
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>CSV / Excel</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu</t>
+          <t>https://www.bfs.admin.ch</t>
         </is>
       </c>
       <c r="O28" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>2026-01 → 2026-07</t>
+          <t>2023 → 2023</t>
         </is>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>QV2, QV4</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>U.S. Food and Drug Administration</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>nombre d'autorisations</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Panorama de la branche medtech suisse</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>QV1, QV3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medical Technology Industry report</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medtech</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>bisannuelle</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>mia CHF</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>https://open.fda.gov</t>
-        </is>
-      </c>
-      <c r="O29" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="P29" s="11" t="inlineStr">
-        <is>
-          <t>2025-09 → 2026-07</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="n">
-        <v>80</v>
-      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.swiss-medtech.ch</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="n"/>
+      <c r="Q29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Indicateur composite avancé (CLI), zone G20</t>
+          <t>Dépôts de brevets en technologies médicales</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -3505,12 +3513,12 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -3519,7 +3527,7 @@
         </is>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
@@ -3528,55 +3536,51 @@
       </c>
       <c r="M30" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="n">
-        <v>882</v>
-      </c>
-      <c r="P30" s="11" t="inlineStr">
-        <is>
-          <t>2023-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q30" s="11" t="n">
-        <v>100</v>
-      </c>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
+          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Office des publications de l'UE</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -3586,12 +3590,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>trimestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>nombre d'avis</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -3607,55 +3611,55 @@
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://ted.europa.eu</t>
         </is>
       </c>
       <c r="O31" s="11" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>2014-T1 → 2026-T3</t>
+          <t>2026-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Production manufacturière suisse (NACE C)</t>
+          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV4</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>U.S. Food and Drug Administration</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -3670,7 +3674,7 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre d'autorisations</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -3678,9 +3682,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K32" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="K32" s="11" t="n"/>
       <c r="L32" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3688,30 +3690,30 @@
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://open.fda.gov</t>
         </is>
       </c>
       <c r="O32" s="11" t="n">
-        <v>192</v>
+        <v>11</v>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2025-09 → 2026-07</t>
         </is>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -3721,7 +3723,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Taux de change CHF/USD et CHF/EUR</t>
+          <t>Indicateur composite avancé (CLI), zone G20</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -3731,12 +3733,12 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3751,7 +3753,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>taux</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
@@ -3760,7 +3762,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
@@ -3769,20 +3771,20 @@
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="O33" s="11" t="n">
-        <v>2752</v>
+        <v>882</v>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2023-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q33" s="11" t="n">
@@ -3792,7 +3794,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -3802,7 +3804,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de marchandises (volume)</t>
+          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -3812,12 +3814,12 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>World Trade Monitor</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -3827,12 +3829,12 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>trimestrielle</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -3840,9 +3842,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K34" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="K34" s="11" t="n"/>
       <c r="L34" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3850,30 +3850,30 @@
       </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O34" s="11" t="n">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2014-T1 → 2026-T3</t>
         </is>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Croissance du PIB mondial</t>
+          <t>Production manufacturière suisse (NACE C)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>World Economic Outlook</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Fonds monétaire international</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>semestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
@@ -3921,7 +3921,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K35" s="11" t="n"/>
+      <c r="K35" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3929,20 +3931,20 @@
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/Publications/WEO</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O35" s="11" t="n">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q35" s="11" t="n">
@@ -3952,7 +3954,7 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -3962,7 +3964,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+          <t>Taux de change CHF/USD et CHF/EUR</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -3972,12 +3974,12 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Taux de change de référence</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Banque nationale suisse</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -3992,7 +3994,7 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>solde d'opinion</t>
+          <t>taux</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
@@ -4000,7 +4002,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K36" s="11" t="n"/>
+      <c r="K36" s="11" t="n">
+        <v>7</v>
+      </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4008,20 +4012,20 @@
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://data.snb.ch</t>
         </is>
       </c>
       <c r="O36" s="11" t="n">
-        <v>468</v>
+        <v>2752</v>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-07</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q36" s="11" t="n">
@@ -4031,7 +4035,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -4041,7 +4045,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF (Suisse)</t>
+          <t>Commerce mondial de marchandises (volume)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -4051,12 +4055,12 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF</t>
+          <t>World Trade Monitor</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>KOF ETH Zurich</t>
+          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -4079,7 +4083,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K37" s="11" t="n"/>
+      <c r="K37" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4087,30 +4093,30 @@
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>https://data.kof.ethz.ch</t>
+          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
         </is>
       </c>
       <c r="O37" s="11" t="n">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2023-01 → 2026-05</t>
         </is>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -4120,7 +4126,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
+          <t>Croissance du PIB mondial</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -4130,12 +4136,12 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>World Economic Outlook</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Fonds monétaire international</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -4145,12 +4151,12 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>semestrielle</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -4166,20 +4172,20 @@
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://www.imf.org/en/Publications/WEO</t>
         </is>
       </c>
       <c r="O38" s="11" t="n">
-        <v>402</v>
+        <v>75</v>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2023 → 2025</t>
         </is>
       </c>
       <c r="Q38" s="11" t="n">
@@ -4189,7 +4195,7 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -4199,7 +4205,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
+          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -4229,7 +4235,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>solde</t>
+          <t>solde d'opinion</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
@@ -4254,7 +4260,7 @@
         </is>
       </c>
       <c r="O39" s="11" t="n">
-        <v>194</v>
+        <v>468</v>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
@@ -4268,7 +4274,7 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -4278,7 +4284,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+          <t>Baromètre conjoncturel KOF (Suisse)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -4288,12 +4294,12 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Baromètre conjoncturel KOF</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>KOF ETH Zurich</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -4303,12 +4309,12 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>trimestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -4324,28 +4330,265 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://data.kof.ethz.ch</t>
         </is>
       </c>
       <c r="O40" s="11" t="n">
-        <v>51</v>
+        <v>387</v>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>2014-T1 → 2026-T3</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q40" s="11" t="n">
         <v>100</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>402</v>
+      </c>
+      <c r="P41" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q41" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>solde</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>194</v>
+      </c>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q42" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>trimestrielle</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="P43" s="11" t="inlineStr">
+        <is>
+          <t>2014-T1 → 2026-T3</t>
+        </is>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q40"/>
+  <autoFilter ref="A1:Q43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4824,10 +5067,10 @@
         </is>
       </c>
       <c r="G12" s="15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -4862,10 +5105,10 @@
         </is>
       </c>
       <c r="G13" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -5307,7 +5550,7 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -5332,7 +5575,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -5702,10 +5945,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -5725,10 +5968,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -6867,7 +7110,11 @@
           <t>09.08.2026</t>
         </is>
       </c>
-      <c r="J12" s="11" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>H7, H8, H9</t>
+        </is>
+      </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
           <t>https://www.fhs.swiss</t>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 14:43</t>
+          <t>24.08.2026 à 15:28</t>
         </is>
       </c>
     </row>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilan'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bilan'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Indicateurs'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instanciation QV'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Instanciation QV'!$1:$1</definedName>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Couverture QV'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lacunes'!$A$1:$H$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lacunes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Sources'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 15:28</t>
+          <t>24.08.2026 à 15:56</t>
         </is>
       </c>
     </row>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>38</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>37</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTA(Indicateurs!$J$2:$J$43)</f>
+        <f>COUNTA(Indicateurs!$J$2:$J$44)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$43,"certifie")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$44,"certifie")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$43,"certifie",Indicateurs!$G$2:$G$43,"hard")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$44,"certifie",Indicateurs!$G$2:$G$44,"hard")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$43,"certifie",Indicateurs!$G$2:$G$43,"composite")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$44,"certifie",Indicateurs!$G$2:$G$44,"composite")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$43,"a_confirmer")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$44,"a_confirmer")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>1089</v>
+        <v>1275</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>570</v>
+        <v>702</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="O9" s="11" t="n">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="O12" s="11" t="n">
-        <v>3513</v>
+        <v>3787</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>677</v>
+        <v>851</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="O14" s="11" t="n">
-        <v>1529</v>
+        <v>1681</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
@@ -2354,38 +2354,38 @@
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Exportations horlogères suisses par marché de destination</t>
+          <t>Brevets en technologies de transport bas carbone (OCDE)</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -2408,40 +2408,38 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K16" s="11" t="n">
-        <v>25</v>
-      </c>
+      <c r="K16" s="11" t="n"/>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="O16" s="11" t="n">
-        <v>31815</v>
+        <v>54</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2014 → 2022</t>
         </is>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -2451,22 +2449,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
+          <t>Exportations horlogères suisses par marché de destination</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -2476,12 +2474,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -2490,39 +2488,39 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O17" s="11" t="n">
-        <v>11</v>
+        <v>40157</v>
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2023-01 → 2026-05</t>
         </is>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -2532,22 +2530,22 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
+          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -2562,7 +2560,7 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
@@ -2571,39 +2569,39 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV / Excel</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.bfs.admin.ch</t>
         </is>
       </c>
       <c r="O18" s="11" t="n">
-        <v>686</v>
+        <v>13</v>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2023 → 2023</t>
         </is>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -2613,22 +2611,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
+          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2643,7 +2641,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -2656,187 +2654,187 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
+          <t>libre_quota</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>838</v>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>2015 → 2025</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>QV4</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Statistiques de propriété intellectuelle</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>OMPI</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>https://www.wipo.int/ipstats</t>
         </is>
       </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="P20" s="11" t="n"/>
+      <c r="Q20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Climat de branche et perspectives</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>QV1, QV5</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Swiss Watch Industry Study</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>composite</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>qualitatif</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="inlineStr">
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="N20" s="13" t="inlineStr">
+      <c r="N21" s="13" t="inlineStr">
         <is>
           <t>https://www.deloitte.com/ch</t>
         </is>
       </c>
-      <c r="O20" s="14" t="inlineStr">
+      <c r="O21" s="14" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>H6</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Horlogerie</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Production horlogère UE (NACE C26.52)</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>QV1</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>Commission européenne</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="n">
-        <v>192</v>
-      </c>
-      <c r="P21" s="11" t="inlineStr">
-        <is>
-          <t>2014-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="n">
-        <v>100</v>
-      </c>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>H6</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -2846,22 +2844,22 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Exportations horlogères suisses, valeur totale (FH)</t>
+          <t>Production horlogère UE (NACE C26.52)</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Statistiques d'exportation horlogère</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Fédération de l'industrie horlogère suisse</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -2876,7 +2874,7 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>mio CHF</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -2885,7 +2883,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
@@ -2894,30 +2892,30 @@
       </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>https://www.fhs.swiss</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O22" s="11" t="n">
-        <v>19</v>
+        <v>492</v>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>2025-01 → 2026-07</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>H8</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -2927,12 +2925,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Exportations de montres mécaniques, valeur (FH)</t>
+          <t>Exportations horlogères suisses, valeur totale (FH)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>QV1, QV2</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -2998,7 +2996,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>H9</t>
+          <t>H8</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -3008,12 +3006,12 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Exportations de montres mécaniques, volume (FH)</t>
+          <t>Exportations de montres mécaniques, valeur (FH)</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV1, QV2</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -3038,7 +3036,7 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>milliers de pièces</t>
+          <t>mio CHF</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -3079,32 +3077,32 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>H9</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
+          <t>Exportations de montres mécaniques, volume (FH)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -3114,12 +3112,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>milliers de pièces</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -3128,39 +3126,39 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>723</v>
+        <v>19</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -3170,22 +3168,22 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
+          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>UN Comtrade — commerce international par code SH</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -3195,12 +3193,12 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -3213,7 +3211,7 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -3223,25 +3221,25 @@
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O26" s="11" t="n">
-        <v>976</v>
+        <v>897</v>
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>2015-01 → 2026-06</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -3251,22 +3249,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -3276,12 +3274,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>pourcentage du PIB</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -3290,7 +3288,7 @@
         </is>
       </c>
       <c r="K27" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -3299,263 +3297,267 @@
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O27" s="11" t="n">
-        <v>3281</v>
+        <v>1252</v>
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2015-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Médical</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>QV2, QV5</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Global Health Expenditure Database</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>OMS</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage du PIB</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>3691</v>
+      </c>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>2023 → 2023</t>
+        </is>
+      </c>
+      <c r="Q28" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Office fédéral de la statistique</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K29" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L29" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M29" s="11" t="inlineStr">
         <is>
           <t>CSV / Excel</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
+      <c r="N29" s="11" t="inlineStr">
         <is>
           <t>https://www.bfs.admin.ch</t>
         </is>
       </c>
-      <c r="O28" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="O29" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P29" s="11" t="inlineStr">
         <is>
           <t>2023 → 2023</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="Q29" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Panorama de la branche medtech suisse</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>QV1, QV3</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Swiss Medical Technology Industry report</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>Swiss Medtech</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>composite</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>bisannuelle</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>mia CHF</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="inlineStr">
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M29" s="13" t="inlineStr">
+      <c r="M30" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="N29" s="13" t="inlineStr">
+      <c r="N30" s="13" t="inlineStr">
         <is>
           <t>https://www.swiss-medtech.ch</t>
         </is>
       </c>
-      <c r="O29" s="14" t="inlineStr">
+      <c r="O30" s="14" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="13" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Dépôts de brevets en technologies médicales</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>QV4</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Statistiques de propriété intellectuelle</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>OMPI</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="N30" s="11" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="11" t="n"/>
+      <c r="P30" s="13" t="n"/>
+      <c r="Q30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -3565,22 +3567,22 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
+          <t>Brevets en technologie médicale, dépôts à l'OEB (OCDE)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Office des publications de l'UE</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -3590,12 +3592,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>nombre d'avis</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -3611,30 +3613,30 @@
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="O31" s="11" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>2026-01 → 2026-07</t>
+          <t>2014 → 2022</t>
         </is>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -3644,22 +3646,22 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
+          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV4</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>U.S. Food and Drug Administration</t>
+          <t>Office des publications de l'UE</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -3674,7 +3676,7 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>nombre d'autorisations</t>
+          <t>nombre d'avis</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -3695,50 +3697,50 @@
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>https://open.fda.gov</t>
+          <t>https://ted.europa.eu</t>
         </is>
       </c>
       <c r="O32" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>2025-09 → 2026-07</t>
+          <t>2026-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Indicateur composite avancé (CLI), zone G20</t>
+          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV4</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>U.S. Food and Drug Administration</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3753,7 +3755,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre d'autorisations</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
@@ -3761,9 +3763,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K33" s="11" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="K33" s="11" t="n"/>
       <c r="L33" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3771,30 +3771,30 @@
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
+          <t>https://open.fda.gov</t>
         </is>
       </c>
       <c r="O33" s="11" t="n">
-        <v>882</v>
+        <v>11</v>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-06</t>
+          <t>2025-09 → 2026-07</t>
         </is>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
+          <t>Indicateur composite avancé (CLI), zone G20</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>trimestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -3842,7 +3842,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K34" s="11" t="n"/>
+      <c r="K34" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3855,25 +3857,25 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="O34" s="11" t="n">
-        <v>51</v>
+        <v>966</v>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>2014-T1 → 2026-T3</t>
+          <t>2023-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -3883,7 +3885,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Production manufacturière suisse (NACE C)</t>
+          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -3908,12 +3910,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>trimestrielle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
@@ -3921,9 +3923,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K35" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="K35" s="11" t="n"/>
       <c r="L35" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="O35" s="11" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2014-T1 → 2026-T3</t>
         </is>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Taux de change CHF/USD et CHF/EUR</t>
+          <t>Production manufacturière suisse (NACE C)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>taux</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
@@ -4012,30 +4012,30 @@
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O36" s="11" t="n">
-        <v>2752</v>
+        <v>492</v>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de marchandises (volume)</t>
+          <t>Taux de change CHF/USD et CHF/EUR</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>World Trade Monitor</t>
+          <t>Taux de change de référence</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+          <t>Banque nationale suisse</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>taux</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
@@ -4093,30 +4093,30 @@
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+          <t>https://data.snb.ch</t>
         </is>
       </c>
       <c r="O37" s="11" t="n">
-        <v>164</v>
+        <v>2924</v>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Croissance du PIB mondial</t>
+          <t>Commerce mondial de marchandises (volume)</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>World Economic Outlook</t>
+          <t>World Trade Monitor</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Fonds monétaire international</t>
+          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>semestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -4164,7 +4164,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K38" s="11" t="n"/>
+      <c r="K38" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4172,30 +4174,30 @@
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/Publications/WEO</t>
+          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
         </is>
       </c>
       <c r="O38" s="11" t="n">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2023-01 → 2026-05</t>
         </is>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -4205,7 +4207,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+          <t>Croissance du PIB mondial</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -4215,12 +4217,12 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>World Economic Outlook</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Fonds monétaire international</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4230,12 +4232,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>semestrielle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>solde d'opinion</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
@@ -4251,30 +4253,30 @@
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://www.imf.org/en/Publications/WEO</t>
         </is>
       </c>
       <c r="O39" s="11" t="n">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-07</t>
+          <t>2023 → 2025</t>
         </is>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -4284,7 +4286,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF (Suisse)</t>
+          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -4294,12 +4296,12 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF</t>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>KOF ETH Zurich</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -4314,7 +4316,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>solde d'opinion</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -4330,30 +4332,30 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>https://data.kof.ethz.ch</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O40" s="11" t="n">
-        <v>387</v>
+        <v>770</v>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -4363,7 +4365,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
+          <t>Baromètre conjoncturel KOF (Suisse)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -4373,12 +4375,12 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Baromètre conjoncturel KOF</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>KOF ETH Zurich</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -4409,30 +4411,30 @@
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://data.kof.ethz.ch</t>
         </is>
       </c>
       <c r="O41" s="11" t="n">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -4442,7 +4444,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
+          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -4472,7 +4474,7 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>solde</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
@@ -4497,21 +4499,21 @@
         </is>
       </c>
       <c r="O42" s="11" t="n">
-        <v>194</v>
+        <v>702</v>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-07</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -4521,7 +4523,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -4546,12 +4548,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>trimestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>solde</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
@@ -4576,19 +4578,98 @@
         </is>
       </c>
       <c r="O43" s="11" t="n">
-        <v>51</v>
+        <v>496</v>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
+          <t>2014-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>trimestrielle</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="n">
+        <v>153</v>
+      </c>
+      <c r="P44" s="11" t="inlineStr">
+        <is>
           <t>2014-T1 → 2026-T3</t>
         </is>
       </c>
-      <c r="Q43" s="11" t="n">
-        <v>100</v>
+      <c r="Q44" s="11" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q43"/>
+  <autoFilter ref="A1:Q44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4991,10 +5072,10 @@
         </is>
       </c>
       <c r="G10" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5625,7 +5706,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5899,10 +5980,10 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -6381,7 +6462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7373,17 +7454,17 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>ofs</t>
+          <t>ocde_brevets</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -7393,7 +7474,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -7413,39 +7494,39 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>H2, M4</t>
+          <t>A7, M6</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>Nomenclature NOGA</t>
+          <t>Jeu DF_PATENTS_OECDSPECIFIC. Dix-huit domaines technologiques, dont MEDICAL et TRA (technologies de transport bas carbone). Sans clé. Vérifié en réponse réelle le 25.08.2026 : 13 points annuels 2010-2022, 106 zones disponibles.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>oica</t>
+          <t>ofs</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>STATENT et statistiques conjoncturelles</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>OICA</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -7455,7 +7536,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>CSV / Excel</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -7480,30 +7561,34 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H2, M4</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="n"/>
+          <t>https://www.bfs.admin.ch</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>Nomenclature NOGA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>ompi</t>
+          <t>oica</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>Statistiques de production automobile</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -7513,7 +7598,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>Tableaux web</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -7538,34 +7623,30 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>H4, M6</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>Classification CIB</t>
-        </is>
-      </c>
+          <t>https://www.oica.net/production-statistics</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>oms_ghed</t>
+          <t>ompi</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -7575,7 +7656,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -7600,40 +7681,44 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="n"/>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>Classification CIB</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>openfda</t>
+          <t>oms_ghed</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>U.S. Food and Drug Administration</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>quotidienne</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -7653,329 +7738,387 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>https://open.fda.gov</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
-        </is>
-      </c>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>openfda</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>U.S. Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>https://open.fda.gov</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>sipri</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Military Expenditure Database</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>SIPRI</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>https://www.sipri.org/databases/milex</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>URL corrigée le 24.08.2026 : l'ancienne (milex.sipri.org) échouait à la négociation TLS. Adresse alignée sur celle de la liaison S4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>sp_global_pmi</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Indices PMI manufacturiers</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Communiqués</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>payant</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>https://www.pmi.spglobal.com</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>Indices détaillés payants ; valeurs de synthèse dans les communiqués</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
+          <t>sp_global_pmi</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Indices PMI manufacturiers</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Communiqués</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>payant</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>https://www.pmi.spglobal.com</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>Indices détaillés payants ; valeurs de synthèse dans les communiqués</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
           <t>swiss_medtech</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Swiss Medical Technology Industry report</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Swiss Medtech</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>bisannuelle</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>https://www.swiss-medtech.ch</t>
         </is>
       </c>
-      <c r="L24" s="13" t="inlineStr">
+      <c r="L25" s="13" t="inlineStr">
         <is>
           <t>Publication bisannuelle, périodes non alignées sur la fenêtre 2023-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>ted</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Office des publications de l'UE</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>quotidienne</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>M7, S7</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>https://ted.europa.eu</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>API de recherche v3, POST JSON, sans clé pour la recherche. Vérifiée en réponse réelle le 20.08.2026 (totalNoticeCount par requête CPV + bornes de dates). Source de la famille OSINT F3 (marchés publics) de la demande de ratification.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>ted</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Office des publications de l'UE</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>M7, S7</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>API de recherche v3, POST JSON, sans clé pour la recherche. Vérifiée en réponse réelle le 20.08.2026 (totalNoticeCount par requête CPV + bornes de dates). Source de la famille OSINT F3 (marchés publics) de la demande de ratification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t>unoosa</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Objets lancés dans l'espace</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>UNOOSA / Our World in Data</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>https://ourworldindata.org/space-exploration-satellites</t>
         </is>
       </c>
-      <c r="L26" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilan'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bilan'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Indicateurs'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instanciation QV'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Instanciation QV'!$1:$1</definedName>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Couverture QV'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lacunes'!$A$1:$H$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lacunes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Sources'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 15:56</t>
+          <t>24.08.2026 à 18:50</t>
         </is>
       </c>
     </row>
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTA(Indicateurs!$J$2:$J$44)</f>
+        <f>COUNTA(Indicateurs!$J$2:$J$46)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$44,"certifie")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$46,"certifie")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$44,"certifie",Indicateurs!$G$2:$G$44,"hard")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$46,"certifie",Indicateurs!$G$2:$G$46,"hard")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$44,"certifie",Indicateurs!$G$2:$G$44,"composite")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$46,"certifie",Indicateurs!$G$2:$G$46,"composite")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$44,"a_confirmer")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$46,"a_confirmer")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4035,7 +4035,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Taux de change CHF/USD et CHF/EUR</t>
+          <t>Brevets en technique de surface et revêtement (OMPI)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>taux</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
@@ -4083,9 +4083,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K37" s="11" t="n">
-        <v>7</v>
-      </c>
+      <c r="K37" s="11" t="n"/>
       <c r="L37" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4093,30 +4091,30 @@
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>ZIP / CSV</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
         </is>
       </c>
       <c r="O37" s="11" t="n">
-        <v>2924</v>
+        <v>161</v>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2000 → 2022</t>
         </is>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -4126,7 +4124,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de marchandises (volume)</t>
+          <t>Brevets en machines-outils (OMPI)</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -4136,12 +4134,12 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>World Trade Monitor</t>
+          <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -4151,12 +4149,12 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -4164,9 +4162,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K38" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="K38" s="11" t="n"/>
       <c r="L38" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4174,30 +4170,30 @@
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>ZIP / CSV</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
         </is>
       </c>
       <c r="O38" s="11" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2000 → 2022</t>
         </is>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -4207,7 +4203,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Croissance du PIB mondial</t>
+          <t>Taux de change CHF/USD et CHF/EUR</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -4217,12 +4213,12 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>World Economic Outlook</t>
+          <t>Taux de change de référence</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Fonds monétaire international</t>
+          <t>Banque nationale suisse</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4232,12 +4228,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>semestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>taux</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
@@ -4245,7 +4241,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K39" s="11" t="n"/>
+      <c r="K39" s="11" t="n">
+        <v>7</v>
+      </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4253,20 +4251,20 @@
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/Publications/WEO</t>
+          <t>https://data.snb.ch</t>
         </is>
       </c>
       <c r="O39" s="11" t="n">
-        <v>81</v>
+        <v>2924</v>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q39" s="11" t="n">
@@ -4276,7 +4274,7 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -4286,7 +4284,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+          <t>Commerce mondial de marchandises (volume)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -4296,12 +4294,12 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>World Trade Monitor</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -4316,7 +4314,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>solde d'opinion</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -4324,7 +4322,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K40" s="11" t="n"/>
+      <c r="K40" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4332,30 +4332,30 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
         </is>
       </c>
       <c r="O40" s="11" t="n">
-        <v>770</v>
+        <v>164</v>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-07</t>
+          <t>2023-01 → 2026-05</t>
         </is>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF (Suisse)</t>
+          <t>Croissance du PIB mondial</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF</t>
+          <t>World Economic Outlook</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>KOF ETH Zurich</t>
+          <t>Fonds monétaire international</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>semestrielle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
@@ -4411,20 +4411,20 @@
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>https://data.kof.ethz.ch</t>
+          <t>https://www.imf.org/en/Publications/WEO</t>
         </is>
       </c>
       <c r="O41" s="11" t="n">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2023 → 2025</t>
         </is>
       </c>
       <c r="Q41" s="11" t="n">
@@ -4434,7 +4434,7 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
+          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>solde d'opinion</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
@@ -4499,11 +4499,11 @@
         </is>
       </c>
       <c r="O42" s="11" t="n">
-        <v>702</v>
+        <v>770</v>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2014-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q42" s="11" t="n">
@@ -4513,7 +4513,7 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
+          <t>Baromètre conjoncturel KOF (Suisse)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Baromètre conjoncturel KOF</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>KOF ETH Zurich</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>solde</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
@@ -4569,20 +4569,20 @@
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://data.kof.ethz.ch</t>
         </is>
       </c>
       <c r="O43" s="11" t="n">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-07</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q43" s="11" t="n">
@@ -4592,7 +4592,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+          <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>trimestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -4657,19 +4657,177 @@
         </is>
       </c>
       <c r="O44" s="11" t="n">
-        <v>153</v>
+        <v>702</v>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>2014-T1 → 2026-T3</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q44" s="11" t="n">
         <v>112</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>solde</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="n">
+        <v>496</v>
+      </c>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q45" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Taux d'utilisation des capacités de l'industrie UE</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>trimestrielle</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="n"/>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>153</v>
+      </c>
+      <c r="P46" s="11" t="inlineStr">
+        <is>
+          <t>2014-T1 → 2026-T3</t>
+        </is>
+      </c>
+      <c r="Q46" s="11" t="n">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q44"/>
+  <autoFilter ref="A1:Q46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5528,10 +5686,10 @@
         </is>
       </c>
       <c r="G22" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -5606,7 +5764,7 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -6256,10 +6414,10 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
@@ -6462,7 +6620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7698,17 +7856,17 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>oms_ghed</t>
+          <t>ompi_tech</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -7718,7 +7876,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>ZIP / CSV</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -7738,45 +7896,49 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>T12, T13</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="n"/>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>Archive wipo-data-patent-indicators.zip, téléchargement direct sans inscription. Comptages par année, office, pays d'origine et domaine technologique (35 domaines). Vérifié en réponse réelle le 25.08.2026 : 663 584 lignes, 2000-2022. Table de concordance CIB/domaine publiée séparément et consultée pour établir les limites de granularité — G04 tombe dans « Techniques de mesure », B64 dans « Transport ».</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>openfda</t>
+          <t>oms_ghed</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>U.S. Food and Drug Administration</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>quotidienne</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -7796,329 +7958,387 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>https://open.fda.gov</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
-        </is>
-      </c>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>openfda</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>U.S. Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>https://open.fda.gov</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
           <t>sipri</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Military Expenditure Database</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>SIPRI</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>https://www.sipri.org/databases/milex</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>URL corrigée le 24.08.2026 : l'ancienne (milex.sipri.org) échouait à la négociation TLS. Adresse alignée sur celle de la liaison S4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>sp_global_pmi</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>Indices PMI manufacturiers</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Communiqués</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>payant</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>https://www.pmi.spglobal.com</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>Indices détaillés payants ; valeurs de synthèse dans les communiqués</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
+          <t>sp_global_pmi</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Indices PMI manufacturiers</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Communiqués</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>payant</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.pmi.spglobal.com</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>Indices détaillés payants ; valeurs de synthèse dans les communiqués</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
           <t>swiss_medtech</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Swiss Medical Technology Industry report</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Swiss Medtech</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>bisannuelle</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>https://www.swiss-medtech.ch</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>Publication bisannuelle, périodes non alignées sur la fenêtre 2023-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>ted</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Office des publications de l'UE</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>quotidienne</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>M7, S7</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>https://ted.europa.eu</t>
-        </is>
-      </c>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>API de recherche v3, POST JSON, sans clé pour la recherche. Vérifiée en réponse réelle le 20.08.2026 (totalNoticeCount par requête CPV + bornes de dates). Source de la famille OSINT F3 (marchés publics) de la demande de ratification.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>ted</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Tenders Electronic Daily — marchés publics UE</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Office des publications de l'UE</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>M7, S7</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>API de recherche v3, POST JSON, sans clé pour la recherche. Vérifiée en réponse réelle le 20.08.2026 (totalNoticeCount par requête CPV + bornes de dates). Source de la famille OSINT F3 (marchés publics) de la demande de ratification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>unoosa</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Objets lancés dans l'espace</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>UNOOSA / Our World in Data</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>https://ourworldindata.org/space-exploration-satellites</t>
         </is>
       </c>
-      <c r="L27" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -117,6 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F7D9D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8E2F2"/>
       </patternFill>
     </fill>
@@ -128,11 +133,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F1F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7D9D5"/>
       </patternFill>
     </fill>
   </fills>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 18:50</t>
+          <t>24.08.2026 à 18:58</t>
         </is>
       </c>
     </row>
@@ -1017,10 +1017,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -1039,10 +1039,10 @@
         <v>45</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -4033,160 +4033,152 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>Brevets en technique de surface et revêtement (OMPI)</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>QV0</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>OMPI</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="15" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="inlineStr">
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>restreint</t>
+        </is>
+      </c>
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="15" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M37" s="11" t="inlineStr">
+      <c r="M37" s="15" t="inlineStr">
         <is>
           <t>ZIP / CSV</t>
         </is>
       </c>
-      <c r="N37" s="11" t="inlineStr">
+      <c r="N37" s="15" t="inlineStr">
         <is>
           <t>https://www.wipo.int/en/web/ip-statistics</t>
         </is>
       </c>
-      <c r="O37" s="11" t="n">
+      <c r="O37" s="15" t="n">
         <v>161</v>
       </c>
-      <c r="P37" s="11" t="inlineStr">
+      <c r="P37" s="15" t="inlineStr">
         <is>
           <t>2000 → 2022</t>
         </is>
       </c>
-      <c r="Q37" s="11" t="n">
+      <c r="Q37" s="15" t="n">
         <v>113</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>T13</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>Brevets en machines-outils (OMPI)</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>QV0</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>OMPI</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K38" s="11" t="n"/>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>restreint</t>
+        </is>
+      </c>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
+      <c r="M38" s="15" t="inlineStr">
         <is>
           <t>ZIP / CSV</t>
         </is>
       </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="N38" s="15" t="inlineStr">
         <is>
           <t>https://www.wipo.int/en/web/ip-statistics</t>
         </is>
       </c>
-      <c r="O38" s="11" t="n">
+      <c r="O38" s="15" t="n">
         <v>161</v>
       </c>
-      <c r="P38" s="11" t="inlineStr">
+      <c r="P38" s="15" t="inlineStr">
         <is>
           <t>2000 → 2022</t>
         </is>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="15" t="n">
         <v>113</v>
       </c>
     </row>
@@ -4895,801 +4887,801 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Santé structurelle</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Les carnets de commandes et les cadences de livraison des avionneurs assurent-ils une charge pluriannuelle à la chaîne de sous-traitance ?</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>Cycle long : le carnet donne une visibilité de plusieurs années, ce qui inverse la logique de veille. On surveille les révisions de cadence annoncées, non les retournements de demande.</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="15" t="n">
+      <c r="H2" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>QV2</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Demande et débouchés</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>La demande de transport aérien soutient-elle le renouvellement des flottes ?</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Le trafic passagers précède les commandes d'appareils de plusieurs trimestres : c'est l'indicateur avancé du cycle civil, en amont du carnet de commandes.</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G3" s="16" t="n">
+      <c r="G3" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="16" t="n">
+      <c r="H3" s="17" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>QV3</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Dynamique géographique</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Quels États accèdent à une capacité spatiale autonome ?</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>L'entrée de nouveaux acteurs nationaux ouvre des chaînes d'approvisionnement nouvelles, mais souvent captives pour raisons de souveraineté. L'opportunité est réelle et l'accès contraint.</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="16" t="n">
+      <c r="H4" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Dynamique technologique</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Quelles ruptures techniques — lanceurs réutilisables, constellations, propulsion alternative — modifient les volumes et les tolérances demandés ?</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>La réutilisabilité réduit le nombre de lanceurs produits tout en durcissant les exigences de qualification ; les constellations inversent la logique du secteur en demandant de la série là où le spatial était unitaire. Deux effets de sens opposé sur le volume de sous-traitance.</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Impulsions publiques</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Les budgets de défense et les budgets spatiaux publics progressent-ils, et sur quels programmes ?</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>La dépense publique EST la demande : défense et spatial institutionnel sont des marchés budgétaires. Une décision budgétaire n'est pas un signal indirect, c'est une commande à venir.</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Santé structurelle</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>La production automobile européenne recule-t-elle plus vite que l'industrie manufacturière dans son ensemble ?</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Cyclicité forte, amplifiée en amont : une variation de production finale se répercute sur les carnets de la sous-traitance avec un effet d'accélérateur. La comparaison à la production manufacturière totale sépare le choc sectoriel du choc conjoncturel.</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="16" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>QV2</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Demande et débouchés</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Les immatriculations et les flux de pièces indiquent-ils une reprise ou une contraction de la demande adressable ?</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Les immatriculations mesurent la demande finale, le commerce de pièces mesure le marché directement adressable par la sous-traitance. Les deux peuvent diverger — un marché stable en véhicules peut se contracter en pièces si le contenu mécanique par véhicule diminue.</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="16" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>QV3</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Dynamique géographique</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Le centre de gravité de la production automobile se déplace-t-il hors d'Europe ?</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>La délocalisation de l'assemblage final entraîne celle des chaînes d'approvisionnement de rang 1 et 2. Menace structurelle sur l'avantage de proximité géographique du sous-traitant européen.</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Dynamique technologique</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>L'électrification recompose-t-elle la demande de composants mécaniques, et à quel rythme selon les marchés ?</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Substitution technologique à effet asymétrique : disparition des familles de pièces liées à la motorisation thermique, apparition de familles nouvelles, et diminution du nombre total de pièces usinées par véhicule. C'est la mutation la plus déterminante du portefeuille pour un décolleteur.</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Impulsions publiques</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Quelles décisions réglementaires — normes d'émission, calendrier d'interdiction du thermique, dispositifs d'incitation — modifient la composition de la demande ?</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>L'action publique ne finance ni n'achète : elle fixe le calendrier de la substitution technologique. Elle agit sur la composition de la demande, non sur son niveau — ce qui explique qu'aucune série statistique budgétaire ne la capte.</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Santé structurelle</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>L'appareil productif horloger suisse se maintient-il en emplois et en établissements, indépendamment du niveau des exportations en valeur ?</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>La branche peut exporter davantage en valeur tout en perdant des établissements : la montée en gamme masque l'érosion du tissu de sous-traitance, qui est précisément le segment concerné par le cas d'illustration.</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="16" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>QV2</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Demande et débouchés</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Vers quels marchés de destination les exportations horlogères se déplacent-elles, et à quel rythme ?</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Demande finale de luxe, très concentrée géographiquement et sensible aux chocs de change et de droits de douane. Elle se transmet à la sous-traitance avec un décalage de quelques mois.</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="16" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>QV3</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Dynamique géographique</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>La production horlogère reste-t-elle concentrée en Suisse, ou des pôles concurrents captent-ils des parts du commerce mondial d'articles d'horlogerie ?</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Concurrence de substitution par le milieu de gamme asiatique. Menace lente mais structurelle sur les volumes de sous-traitance, invisible dans les seules statistiques suisses.</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Dynamique technologique</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>La montre connectée et les nouveaux matériaux recomposent-ils la demande de composants mécaniques ?</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Substitution technologique partielle : le produit connecté ne remplace pas le luxe mécanique mais comprime l'entrée de gamme, segment à fort volume de pièces usinées.</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Impulsions publiques</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Quelles décisions publiques — droits de douane, accords commerciaux, réglementation Swiss made — modifient les conditions d'accès aux marchés ?</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>L'action publique n'est ici ni acheteuse ni finançante : elle agit sur les conditions d'accès et les règles d'origine, donc sur les prix relatifs et non sur le niveau de la demande. Le choc douanier de 2025 constitue l'exception qui rend la question observable.</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>marginale</t>
         </is>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Santé structurelle</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>La base productive medtech européenne et suisse croît-elle en volume et en emplois ?</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Secteur défensif, peu cyclique : la production suit la demande démographique. Tout décrochage est donc un signal structurel et non une fluctuation conjoncturelle.</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>QV2</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Demande et débouchés</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Quels pays accroissent leurs importations d'instruments médicaux, et leurs dépenses de santé le confirment-elles ?</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Demande solvabilisée par les systèmes de santé : le budget public précède la commande hospitalière avec un décalage long. Le croisement des deux séries distingue la croissance financée de la croissance annoncée.</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="16" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>QV3</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Dynamique géographique</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Où se localise la production d'instruments médicaux, et la position suisse s'y érode-t-elle ?</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Les barrières réglementaires (MDR européen, homologation FDA) freinent les délocalisations : la géographie bouge lentement, ce qui rend tout mouvement observé significatif.</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Dynamique technologique</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Quelles mutations techniques — chirurgie mini-invasive, robotique, implants personnalisés — recomposent la demande de pièces de précision ?</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Chaque génération d'instruments modifie les tolérances, les matériaux et les volumes demandés au sous-traitant. L'antériorité du signal se lit dans les dépôts de brevets, plusieurs années avant la commande.</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Médical</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Impulsions publiques</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Comment évoluent les dépenses publiques de santé, et quels programmes d'équipement en découlent ?</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>Déterminant médiatisé : la dépense publique solvabilise la demande hospitalière sans être elle-même la commande. Décalage de plusieurs années entre arbitrage budgétaire et appel d'offres.</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>significative</t>
         </is>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="16" t="n">
+      <c r="H21" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>QV0</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Attribution</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Le mouvement observé sur un secteur est-il propre à ce secteur, ou porté par la conjoncture générale ?</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Sans référentiel commun, un recul sectoriel est ininterprétable : une baisse des exportations ne se lit pas de la même manière selon que le commerce mondial recule ou progresse. Le socle transversal fournit le dénominateur de l'attribution.</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>13</v>
+      <c r="G22" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -5764,7 +5756,7 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -6012,23 +6004,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>aerospatial</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>non couverte</t>
         </is>
@@ -6150,23 +6142,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>automobile</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>non couverte</t>
         </is>
@@ -6414,10 +6406,10 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
@@ -6494,76 +6486,76 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Dynamique technologique</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Quelles ruptures techniques — lanceurs réutilisables, constellations, propulsion alternative — modifient les volumes et les tolérances demandés ?</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n">
+      <c r="F2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="18" t="n">
+      <c r="G2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>lacune — aucun indicateur</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Impulsions publiques</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Quelles décisions réglementaires — normes d'émission, calendrier d'interdiction du thermique, dispositifs d'incitation — modifient la composition de la demande ?</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>lacune — aucun indicateur</t>
         </is>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 18:58</t>
+          <t>24.08.2026 à 19:49</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>1275</v>
+        <v>1740</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="O5" s="11" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Q5" s="11" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>702</v>
+        <v>1032</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -1783,15 +1783,15 @@
         </is>
       </c>
       <c r="O8" s="11" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>2025-09 → 2026-07</t>
+          <t>2025-08 → 2026-07</t>
         </is>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="O9" s="11" t="n">
-        <v>492</v>
+        <v>1242</v>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="O12" s="11" t="n">
-        <v>3787</v>
+        <v>4472</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>851</v>
+        <v>1286</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="O14" s="11" t="n">
-        <v>1681</v>
+        <v>2061</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>492</v>
+        <v>1242</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="O16" s="11" t="n">
-        <v>54</v>
+        <v>324</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="O17" s="11" t="n">
-        <v>40157</v>
+        <v>61012</v>
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="O18" s="11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="O19" s="11" t="n">
-        <v>838</v>
+        <v>1218</v>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="O22" s="11" t="n">
-        <v>492</v>
+        <v>1242</v>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="O23" s="11" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="O24" s="11" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="O26" s="11" t="n">
-        <v>897</v>
+        <v>1332</v>
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="O27" s="11" t="n">
-        <v>1252</v>
+        <v>1942</v>
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="O28" s="11" t="n">
-        <v>3691</v>
+        <v>4101</v>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29">
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="O29" s="11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="Q29" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="O31" s="11" t="n">
-        <v>54</v>
+        <v>324</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32">
@@ -3701,15 +3701,15 @@
         </is>
       </c>
       <c r="O32" s="11" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>2026-01 → 2026-07</t>
+          <t>2025-08 → 2026-07</t>
         </is>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33">
@@ -3780,15 +3780,15 @@
         </is>
       </c>
       <c r="O33" s="11" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>2025-09 → 2026-07</t>
+          <t>2025-08 → 2026-07</t>
         </is>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="O34" s="11" t="n">
-        <v>966</v>
+        <v>1176</v>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="O35" s="11" t="n">
-        <v>153</v>
+        <v>408</v>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="O36" s="11" t="n">
-        <v>492</v>
+        <v>1242</v>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="O39" s="11" t="n">
-        <v>2924</v>
+        <v>3354</v>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="O40" s="11" t="n">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="O41" s="11" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="O42" s="11" t="n">
-        <v>770</v>
+        <v>1525</v>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="O43" s="11" t="n">
-        <v>473</v>
+        <v>688</v>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="Q43" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="O44" s="11" t="n">
-        <v>702</v>
+        <v>1452</v>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Q44" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="O45" s="11" t="n">
-        <v>496</v>
+        <v>1251</v>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="O46" s="11" t="n">
-        <v>153</v>
+        <v>408</v>
       </c>
       <c r="P46" s="11" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Q46" s="11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 19:49</t>
+          <t>24.08.2026 à 21:12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>1740</v>
+        <v>2033</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="O5" s="11" t="n">
-        <v>561</v>
+        <v>825</v>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Q5" s="11" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>1032</v>
+        <v>1230</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="O8" s="11" t="n">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="O9" s="11" t="n">
-        <v>1242</v>
+        <v>1692</v>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="O12" s="11" t="n">
-        <v>4472</v>
+        <v>5084</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>1286</v>
+        <v>1547</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="O14" s="11" t="n">
-        <v>2061</v>
+        <v>2436</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>1242</v>
+        <v>1692</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="O16" s="11" t="n">
-        <v>324</v>
+        <v>486</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -2506,15 +2506,15 @@
         </is>
       </c>
       <c r="O17" s="11" t="n">
-        <v>61012</v>
+        <v>77795</v>
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2023-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18">
@@ -2587,15 +2587,15 @@
         </is>
       </c>
       <c r="O18" s="11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2021 → 2024</t>
         </is>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="O19" s="11" t="n">
-        <v>1218</v>
+        <v>1446</v>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="O22" s="11" t="n">
-        <v>1242</v>
+        <v>1692</v>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="O23" s="11" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="O24" s="11" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="O26" s="11" t="n">
-        <v>1332</v>
+        <v>1593</v>
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="O27" s="11" t="n">
-        <v>1942</v>
+        <v>2356</v>
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="O28" s="11" t="n">
-        <v>4101</v>
+        <v>4716</v>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
@@ -3468,15 +3468,15 @@
         </is>
       </c>
       <c r="O29" s="11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2023</t>
+          <t>2021 → 2024</t>
         </is>
       </c>
       <c r="Q29" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="O31" s="11" t="n">
-        <v>324</v>
+        <v>486</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="O32" s="11" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33">
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="O33" s="11" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="O34" s="11" t="n">
-        <v>1176</v>
+        <v>1302</v>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="O35" s="11" t="n">
-        <v>408</v>
+        <v>561</v>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="O36" s="11" t="n">
-        <v>1242</v>
+        <v>1692</v>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="O39" s="11" t="n">
-        <v>3354</v>
+        <v>3612</v>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="O40" s="11" t="n">
-        <v>205</v>
+        <v>287</v>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="O41" s="11" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="O42" s="11" t="n">
-        <v>1525</v>
+        <v>1978</v>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="O43" s="11" t="n">
-        <v>688</v>
+        <v>817</v>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="Q43" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="O44" s="11" t="n">
-        <v>1452</v>
+        <v>1902</v>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Q44" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="O45" s="11" t="n">
-        <v>1251</v>
+        <v>1704</v>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="O46" s="11" t="n">
-        <v>408</v>
+        <v>561</v>
       </c>
       <c r="P46" s="11" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Q46" s="11" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilan'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bilan'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicateurs'!$A$1:$Q$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Indicateurs'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instanciation QV'!$A$1:$H$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Instanciation QV'!$1:$1</definedName>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Couverture QV'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lacunes'!$A$1:$H$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lacunes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Sources'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +93,7 @@
       <sz val="15"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -130,11 +130,6 @@
         <fgColor rgb="00F2F0F7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F1F3"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -162,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -207,9 +202,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,7 +632,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24.08.2026 à 21:12</t>
+          <t>02.09.2026 à 07:55</t>
         </is>
       </c>
     </row>
@@ -926,7 +918,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>6</v>
@@ -938,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -948,19 +940,19 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -970,19 +962,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="n">
         <v>9</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>8</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1036,19 +1028,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>38</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1072,7 +1064,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTA(Indicateurs!$J$2:$J$46)</f>
+        <f>COUNTA(Indicateurs!$J$2:$J$54)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1075,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$46,"certifie")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$54,"certifie")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1086,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$46,"certifie",Indicateurs!$G$2:$G$46,"hard")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$54,"certifie",Indicateurs!$G$2:$G$54,"hard")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1097,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS(Indicateurs!$J$2:$J$46,"certifie",Indicateurs!$G$2:$G$46,"composite")</f>
+        <f>COUNTIFS(Indicateurs!$J$2:$J$54,"certifie",Indicateurs!$G$2:$G$54,"composite")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1108,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF(Indicateurs!$J$2:$J$46,"a_confirmer")</f>
+        <f>COUNTIF(Indicateurs!$J$2:$J$54,"a_confirmer")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1151,7 +1143,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
@@ -1467,7 +1459,7 @@
         </is>
       </c>
       <c r="O4" s="11" t="n">
-        <v>2033</v>
+        <v>2833</v>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1467,7 @@
         </is>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -1657,7 +1649,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>UN Comtrade : commerce international par code SH</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1704,7 +1696,7 @@
         </is>
       </c>
       <c r="O7" s="11" t="n">
-        <v>1230</v>
+        <v>1758</v>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1712,7 +1704,7 @@
         </is>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
@@ -1738,7 +1730,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
+          <t>Tenders Electronic Daily : marchés publics UE</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -1783,15 +1775,15 @@
         </is>
       </c>
       <c r="O8" s="11" t="n">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>2025-08 → 2026-07</t>
+          <t>2025-08 → 2026-08</t>
         </is>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
@@ -1817,7 +1809,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1864,7 +1856,7 @@
         </is>
       </c>
       <c r="O9" s="11" t="n">
-        <v>1692</v>
+        <v>2892</v>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
@@ -1872,90 +1864,92 @@
         </is>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Automobile</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Production mondiale de véhicules par pays</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>QV1, QV3</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Statistiques de production automobile</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>OICA</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>unités</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Aérospatial</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement : dynamique technologique (triage IA des flux)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>QV4</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement dans les flux qualifiés (dérivation interne)</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Dispositif de veille : dérivation du triage IA (v_intensite_signalement)</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>Tableaux web</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="n"/>
-      <c r="Q10" s="11" t="n"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>interne : flux_sources → flux_items → flux_triage_ia → v_intensite_signalement</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>2026-08 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -1965,22 +1959,22 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Immatriculations de véhicules neufs en Europe</t>
+          <t>Production mondiale de véhicules par pays</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1, QV3</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Immatriculations de véhicules neufs</t>
+          <t>Statistiques de production automobile</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>ACEA</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1990,7 +1984,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -2013,111 +2007,109 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>Tableaux web</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>https://www.acea.auto</t>
+          <t>https://www.oica.net/production-statistics</t>
         </is>
       </c>
       <c r="O11" s="11" t="n">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>2025-11 → 2026-06</t>
+          <t>2021 → 2024</t>
         </is>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>64</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Ventes mondiales de véhicules électriques par pays</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>QV2, QV3, QV4</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Global EV Data Explorer</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Agence internationale de l'énergie</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>unités</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement : impulsions publiques (triage IA des flux)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>QV5</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement dans les flux qualifiés (dérivation interne)</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Dispositif de veille : dérivation du triage IA (v_intensite_signalement)</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>https://www.iea.org</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>5084</v>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>2023 → 2025</t>
-        </is>
-      </c>
-      <c r="Q12" s="11" t="n">
-        <v>150</v>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>interne : flux_sources → flux_items → flux_triage_ia → v_intensite_signalement</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" s="13" t="inlineStr">
+        <is>
+          <t>2026-07 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -2127,22 +2119,22 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de parties et accessoires automobiles (SH 8708)</t>
+          <t>Part électrique des ventes mondiales de voitures (IEA)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Global EV Data Explorer</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Agence internationale de l'énergie</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -2157,7 +2149,7 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -2165,40 +2157,38 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K13" s="11" t="n">
-        <v>10</v>
-      </c>
+      <c r="K13" s="11" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://www.iea.org</t>
         </is>
       </c>
       <c r="O13" s="11" t="n">
-        <v>1547</v>
+        <v>5320</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2014 → 2025</t>
         </is>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -2208,27 +2198,27 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Production industrielle automobile UE (NACE C29)</t>
+          <t>Immatriculations de voitures particulières neuves, UE27 (ACEA)</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Immatriculations de véhicules neufs</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>ACEA</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -2238,7 +2228,7 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>unités</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -2247,7 +2237,7 @@
         </is>
       </c>
       <c r="K14" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
@@ -2256,30 +2246,30 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://www.acea.auto</t>
         </is>
       </c>
       <c r="O14" s="11" t="n">
-        <v>2436</v>
+        <v>8</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2025-11 → 2026-06</t>
         </is>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>150</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -2289,22 +2279,22 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Production d'équipements automobiles UE (NACE C29.3)</t>
+          <t>Ventes mondiales de véhicules électriques par pays</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>QV1, QV2</t>
+          <t>QV2, QV3, QV4</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Global EV Data Explorer</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Agence internationale de l'énergie</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -2314,12 +2304,12 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>unités</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
@@ -2328,7 +2318,7 @@
         </is>
       </c>
       <c r="K15" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
@@ -2337,30 +2327,30 @@
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://www.iea.org</t>
         </is>
       </c>
       <c r="O15" s="11" t="n">
-        <v>1692</v>
+        <v>10452</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-06</t>
+          <t>2014 → 2025</t>
         </is>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -2370,22 +2360,22 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Brevets en technologies de transport bas carbone (OCDE)</t>
+          <t>Commerce mondial de parties et accessoires automobiles (SH 8708)</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Brevets par domaine technologique</t>
+          <t>UN Comtrade : commerce international par code SH</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -2400,7 +2390,7 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -2408,63 +2398,65 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K16" s="11" t="n"/>
+      <c r="K16" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>API SDMX</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O16" s="11" t="n">
-        <v>486</v>
+        <v>2243</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>2014 → 2022</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Exportations horlogères suisses par marché de destination</t>
+          <t>Production industrielle automobile UE (NACE C29)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>QV2</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -2479,7 +2471,7 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -2488,11 +2480,11 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -2502,50 +2494,50 @@
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O17" s="11" t="n">
-        <v>77795</v>
+        <v>3628</v>
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Emploi et établissements de la branche horlogère (NOGA 26.52)</t>
+          <t>Production d'équipements automobiles UE (NACE C29.3)</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV1, QV2</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -2555,12 +2547,12 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
@@ -2569,7 +2561,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
@@ -2578,55 +2570,55 @@
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O18" s="11" t="n">
-        <v>30</v>
+        <v>2892</v>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>2021 → 2024</t>
+          <t>2014-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
+          <t>Brevets en technologies de transport bas carbone (OCDE)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2641,7 +2633,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -2650,141 +2642,139 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="O19" s="11" t="n">
-        <v>1446</v>
+        <v>918</v>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2014 → 2022</t>
         </is>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Horlogerie</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>QV4</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Statistiques de propriété intellectuelle</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>OMPI</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Automobile</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Avis de marchés publics UE en pièces mécaniques automobiles (TED, CPV 34.31/34.32)</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>QV2, QV5</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Tenders Electronic Daily : marchés publics UE</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Office des publications de l'UE</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>nombre d'avis</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>https://ted.europa.eu</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
         <is>
           <t>aucune collecte</t>
         </is>
       </c>
-      <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="11" t="n"/>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Horlogerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Climat de branche et perspectives</t>
+          <t>Intensité de signalement : dynamique technologique (triage IA des flux)</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>QV1, QV5</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Swiss Watch Industry Study</t>
+          <t>Intensité de signalement dans les flux qualifiés (dérivation interne)</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dispositif de veille : dérivation du triage IA (v_intensite_signalement)</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -2794,12 +2784,12 @@
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>qualitatif</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
@@ -2815,26 +2805,30 @@
       </c>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>https://www.deloitte.com/ch</t>
-        </is>
-      </c>
-      <c r="O21" s="14" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="13" t="n"/>
+          <t>interne : flux_sources → flux_items → flux_triage_ia → v_intensite_signalement</t>
+        </is>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" s="13" t="inlineStr">
+        <is>
+          <t>2026-07 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>H6</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -2844,240 +2838,238 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Production horlogère UE (NACE C26.52)</t>
+          <t>Exportations horlogères suisses par marché de destination</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
+          <t>QV2</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>UN Comtrade : commerce international par code SH</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Nations Unies</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>libre_quota</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>https://comtradeplus.un.org</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>124535</v>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-07</t>
+        </is>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement : dynamique technologique (triage IA des flux)</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>QV4</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement dans les flux qualifiés (dérivation interne)</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Dispositif de veille : dérivation du triage IA (v_intensite_signalement)</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>interne : flux_sources → flux_items → flux_triage_ia → v_intensite_signalement</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="13" t="inlineStr">
+        <is>
+          <t>2026-08 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q23" s="13" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Entreprises de la branche horlogère et microtechnique suisse (recensement CP)</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Commission européenne</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Recensement du personnel et des entreprises des industries horlogère et microtechnique suisses</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Convention patronale de l'industrie horlogère suisse</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>1692</v>
-      </c>
-      <c r="P22" s="11" t="inlineStr">
-        <is>
-          <t>2014-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q22" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Horlogerie</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Exportations horlogères suisses, valeur totale (FH)</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>QV2</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Statistiques d'exportation horlogère</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Fédération de l'industrie horlogère suisse</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>mio CHF</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>PDF / communiqués</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fhs.swiss</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="P23" s="11" t="inlineStr">
-        <is>
-          <t>2025-01 → 2026-07</t>
-        </is>
-      </c>
-      <c r="Q23" s="11" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>H8</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Horlogerie</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Exportations de montres mécaniques, valeur (FH)</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>QV1, QV2</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Statistiques d'exportation horlogère</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Fédération de l'industrie horlogère suisse</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>mio CHF</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>certifie</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>PDF / communiqués</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fhs.swiss</t>
-        </is>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>2025-01 → 2026-07</t>
-        </is>
-      </c>
-      <c r="Q24" s="11" t="n">
-        <v>152</v>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>PDF (lecture multimodale)</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>https://cpih.ch/statistiques/</t>
+        </is>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="P24" s="13" t="inlineStr">
+        <is>
+          <t>2013 → 2025</t>
+        </is>
+      </c>
+      <c r="Q24" s="13" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>H9</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -3087,7 +3079,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Exportations de montres mécaniques, volume (FH)</t>
+          <t>Emplois horlogers suisses (STATENT, NOGA 26.52)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -3097,12 +3089,12 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Statistiques d'exportation horlogère</t>
+          <t>STATENT : Etablissements et emplois selon année, canton, genre économique et unité d'observation (table px-x-0602010000_103)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Fédération de l'industrie horlogère suisse</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -3112,12 +3104,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>milliers de pièces</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -3126,7 +3118,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
@@ -3135,60 +3127,60 @@
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>API PX-Web (JSON-stat2, requête POST)</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://www.fhs.swiss</t>
+          <t>https://www.pxweb.bfs.admin.ch/api/v1/fr/px-x-0602010000_103/px-x-0602010000_103.px</t>
         </is>
       </c>
       <c r="O25" s="11" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>2025-01 → 2026-07</t>
+          <t>2014 → 2024</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>152</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
+          <t>Emploi de la branche horlogère et microtechnique suisse (recensement CP)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV3</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>Recensement du personnel et des entreprises des industries horlogère et microtechnique suisses</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Convention patronale de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -3198,7 +3190,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -3207,64 +3199,64 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>PDF (lecture multimodale)</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://cpih.ch/statistiques/</t>
         </is>
       </c>
       <c r="O26" s="11" t="n">
-        <v>1593</v>
+        <v>117</v>
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>2015 → 2025</t>
+          <t>2005 → 2025</t>
         </is>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Production de l'industrie manufacturière diverse UE (NACE C32, dont instruments médicaux C32.5)</t>
+          <t>Commerce mondial d'articles d'horlogerie (SH ch. 91), par pays</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>QV1</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>UN Comtrade : commerce international par code SH</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -3274,12 +3266,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -3288,11 +3280,11 @@
         </is>
       </c>
       <c r="K27" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -3302,50 +3294,50 @@
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O27" s="11" t="n">
-        <v>2356</v>
+        <v>2054</v>
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>2015-01 → 2026-06</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
+          <t>Dépôts de brevets en horlogerie (CIB G04)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -3360,7 +3352,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>pourcentage du PIB</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -3369,7 +3361,7 @@
         </is>
       </c>
       <c r="K28" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
@@ -3378,211 +3370,207 @@
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="n">
-        <v>4716</v>
-      </c>
-      <c r="P28" s="11" t="inlineStr">
-        <is>
-          <t>2023 → 2023</t>
-        </is>
-      </c>
-      <c r="Q28" s="11" t="n">
-        <v>150</v>
-      </c>
+          <t>https://www.wipo.int/ipstats</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Emploi et établissements medtech suisses (NOGA 32.5, 26.6)</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Climat de branche et perspectives</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>QV1, QV5</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Watch Industry Study</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>qualitatif</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/ch</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="n"/>
+      <c r="Q29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Horlogerie</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Production horlogère UE (NACE C26.52)</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>QV1</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>STATENT et statistiques conjoncturelles</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>Office fédéral de la statistique</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K29" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="K30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>CSV / Excel</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>https://www.bfs.admin.ch</t>
-        </is>
-      </c>
-      <c r="O29" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P29" s="11" t="inlineStr">
-        <is>
-          <t>2021 → 2024</t>
-        </is>
-      </c>
-      <c r="Q29" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Médical</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Panorama de la branche medtech suisse</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>QV1, QV3</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medical Technology Industry report</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Medtech</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>composite</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>bisannuelle</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>mia CHF</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N30" s="13" t="inlineStr">
-        <is>
-          <t>https://www.swiss-medtech.ch</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>aucune collecte</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="n">
+        <v>2892</v>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q30" s="11" t="n">
+        <v>214</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Brevets en technologie médicale, dépôts à l'OEB (OCDE)</t>
+          <t>Exportations suisses de montres-bracelets, valeur (FH)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>QV4</t>
+          <t>QV2</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Brevets par domaine technologique</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -3592,12 +3580,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>mio CHF</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -3605,7 +3593,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K31" s="11" t="n"/>
+      <c r="K31" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3613,55 +3603,55 @@
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>API SDMX</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O31" s="11" t="n">
-        <v>486</v>
+        <v>95</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>2014 → 2022</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>H8</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
+          <t>Exportations de montres mécaniques, valeur (FH)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV5</t>
+          <t>QV1, QV2</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Office des publications de l'UE</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -3676,7 +3666,7 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>nombre d'avis</t>
+          <t>mio CHF</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -3684,7 +3674,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K32" s="11" t="n"/>
+      <c r="K32" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3692,55 +3684,55 @@
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>https://ted.europa.eu</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O32" s="11" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>2025-08 → 2026-07</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>H9</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Médical</t>
+          <t>Horlogerie</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
+          <t>Exportations de montres mécaniques, volume (FH)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>QV2, QV4</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+          <t>Statistiques d'exportation horlogère</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>U.S. Food and Drug Administration</t>
+          <t>Fédération de l'industrie horlogère suisse</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3755,7 +3747,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>nombre d'autorisations</t>
+          <t>milliers de pièces</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
@@ -3763,7 +3755,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K33" s="11" t="n"/>
+      <c r="K33" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3771,12 +3765,12 @@
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>PDF / communiqués</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>https://open.fda.gov</t>
+          <t>https://www.fhs.swiss</t>
         </is>
       </c>
       <c r="O33" s="11" t="n">
@@ -3784,42 +3778,42 @@
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>2025-08 → 2026-07</t>
+          <t>2025-01 → 2026-07</t>
         </is>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Indicateur composite avancé (CLI), zone G20</t>
+          <t>Commerce mondial d'instruments médicaux (SH 9018-9022), par pays</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV3</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>UN Comtrade : commerce international par code SH</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -3829,12 +3823,12 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -3843,11 +3837,11 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr">
@@ -3857,45 +3851,45 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="O34" s="11" t="n">
-        <v>1302</v>
+        <v>2289</v>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-06</t>
+          <t>2015 → 2025</t>
         </is>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
+          <t>Production d'instruments et fournitures médicales et dentaires UE (NACE C32.5)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV1</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3910,12 +3904,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>trimestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
@@ -3923,7 +3917,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K35" s="11" t="n"/>
+      <c r="K35" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -3940,46 +3936,46 @@
         </is>
       </c>
       <c r="O35" s="11" t="n">
-        <v>561</v>
+        <v>3460</v>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>2014-T1 → 2026-T3</t>
+          <t>2015-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Production manufacturière suisse (NACE C)</t>
+          <t>Dépenses de santé par pays (part du PIB et par habitant)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
@@ -3989,12 +3985,12 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>pourcentage du PIB</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
@@ -4003,214 +3999,220 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr">
+        <is>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>9843</v>
+      </c>
+      <c r="P36" s="11" t="inlineStr">
+        <is>
+          <t>2014 → 2023</t>
+        </is>
+      </c>
+      <c r="Q36" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Médical</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Emplois medtech et mécanique de précision en Suisse (NOGA 26.6, 32.5 — y c. mécaniciens-dentistes et lunetterie)</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>QV1</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>STATENT : Etablissements et emplois selon année, canton, genre économique et unité d'observation (table px-x-0602010000_103)</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Office fédéral de la statistique</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="L37" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M36" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="N36" s="11" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
-        </is>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>1692</v>
-      </c>
-      <c r="P36" s="11" t="inlineStr">
-        <is>
-          <t>2014-01 → 2026-06</t>
-        </is>
-      </c>
-      <c r="Q36" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Socle transversal</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>Brevets en technique de surface et revêtement (OMPI)</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Indicateurs de brevets par domaine technologique</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>OMPI</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>restreint</t>
-        </is>
-      </c>
-      <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="inlineStr">
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>API PX-Web (JSON-stat2, requête POST)</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pxweb.bfs.admin.ch/api/v1/fr/px-x-0602010000_103/px-x-0602010000_103.px</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="P37" s="11" t="inlineStr">
+        <is>
+          <t>2014 → 2024</t>
+        </is>
+      </c>
+      <c r="Q37" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Médical</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Panorama de la branche medtech suisse</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>QV1, QV3</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medical Technology Industry report</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Medtech</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>bisannuelle</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>mia CHF</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M37" s="15" t="inlineStr">
-        <is>
-          <t>ZIP / CSV</t>
-        </is>
-      </c>
-      <c r="N37" s="15" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/en/web/ip-statistics</t>
-        </is>
-      </c>
-      <c r="O37" s="15" t="n">
-        <v>161</v>
-      </c>
-      <c r="P37" s="15" t="inlineStr">
-        <is>
-          <t>2000 → 2022</t>
-        </is>
-      </c>
-      <c r="Q37" s="15" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Socle transversal</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Brevets en machines-outils (OMPI)</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Indicateurs de brevets par domaine technologique</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>OMPI</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>restreint</t>
-        </is>
-      </c>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="M38" s="15" t="inlineStr">
-        <is>
-          <t>ZIP / CSV</t>
-        </is>
-      </c>
-      <c r="N38" s="15" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/en/web/ip-statistics</t>
-        </is>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>161</v>
-      </c>
-      <c r="P38" s="15" t="inlineStr">
-        <is>
-          <t>2000 → 2022</t>
-        </is>
-      </c>
-      <c r="Q38" s="15" t="n">
-        <v>113</v>
-      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.swiss-medtech.ch</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr">
+        <is>
+          <t>aucune collecte</t>
+        </is>
+      </c>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Taux de change CHF/USD et CHF/EUR</t>
+          <t>Brevets en technologie médicale, dépôts à l'OEB (OCDE)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV4</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4220,12 +4222,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>taux</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
@@ -4234,7 +4236,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
@@ -4243,55 +4245,55 @@
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="O39" s="11" t="n">
-        <v>3612</v>
+        <v>918</v>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014 → 2022</t>
         </is>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Commerce mondial de marchandises (volume)</t>
+          <t>Avis de marchés publics UE en équipements médicaux (TED, CPV 33)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV5</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>World Trade Monitor</t>
+          <t>Tenders Electronic Daily : marchés publics UE</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+          <t>Office des publications de l'UE</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -4306,7 +4308,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>nombre d'avis</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -4314,9 +4316,7 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K40" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="K40" s="11" t="n"/>
       <c r="L40" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4324,55 +4324,55 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+          <t>https://ted.europa.eu</t>
         </is>
       </c>
       <c r="O40" s="11" t="n">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-05</t>
+          <t>2025-08 → 2026-08</t>
         </is>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>151</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Socle transversal</t>
+          <t>Médical</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Croissance du PIB mondial</t>
+          <t>Autorisations FDA 510(k) de dispositifs médicaux (États-Unis)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>QV0</t>
+          <t>QV2, QV4</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>World Economic Outlook</t>
+          <t>openFDA : bases publiques de la Food and Drug Administration</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Fonds monétaire international</t>
+          <t>U.S. Food and Drug Administration</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>semestrielle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>pourcentage</t>
+          <t>nombre d'autorisations</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
@@ -4403,30 +4403,30 @@
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>API</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/Publications/WEO</t>
+          <t>https://open.fda.gov</t>
         </is>
       </c>
       <c r="O41" s="11" t="n">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>2023 → 2025</t>
+          <t>2025-08 → 2026-08</t>
         </is>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+          <t>Indicateur composite avancé (CLI), zone G20</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Commission européenne</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>solde d'opinion</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
@@ -4474,7 +4474,9 @@
           <t>certifie</t>
         </is>
       </c>
-      <c r="K42" s="11" t="n"/>
+      <c r="K42" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
           <t>libre</t>
@@ -4487,25 +4489,25 @@
       </c>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="O42" s="11" t="n">
-        <v>1978</v>
+        <v>1638</v>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>2014-01 → 2026-07</t>
+          <t>2023-01 → 2026-06</t>
         </is>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -4515,7 +4517,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF (Suisse)</t>
+          <t>Part des industriels déclarant la demande comme facteur limitant (UE)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -4525,12 +4527,12 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Baromètre conjoncturel KOF</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>KOF ETH Zurich</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -4540,12 +4542,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>trimestrielle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>pourcentage</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
@@ -4561,265 +4563,901 @@
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>https://data.kof.ethz.ch</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="O43" s="11" t="n">
-        <v>817</v>
+        <v>969</v>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>2023-01 → 2026-07</t>
+          <t>2014-T1 → 2026-T3</t>
         </is>
       </c>
       <c r="Q43" s="11" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Production manufacturière suisse (NACE C)</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="n">
+        <v>2892</v>
+      </c>
+      <c r="P44" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-06</t>
+        </is>
+      </c>
+      <c r="Q44" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Brevets en technique de surface et revêtement (OMPI)</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Indicateurs de brevets par domaine technologique</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>OMPI</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="J45" s="15" t="inlineStr">
+        <is>
+          <t>restreint</t>
+        </is>
+      </c>
+      <c r="K45" s="15" t="n"/>
+      <c r="L45" s="15" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M45" s="15" t="inlineStr">
+        <is>
+          <t>ZIP / CSV</t>
+        </is>
+      </c>
+      <c r="N45" s="15" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="P45" s="15" t="inlineStr">
+        <is>
+          <t>2000 → 2022</t>
+        </is>
+      </c>
+      <c r="Q45" s="15" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Brevets en machines-outils (OMPI)</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Indicateurs de brevets par domaine technologique</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>OMPI</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="J46" s="15" t="inlineStr">
+        <is>
+          <t>restreint</t>
+        </is>
+      </c>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M46" s="15" t="inlineStr">
+        <is>
+          <t>ZIP / CSV</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
+        </is>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="P46" s="15" t="inlineStr">
+        <is>
+          <t>2000 → 2022</t>
+        </is>
+      </c>
+      <c r="Q46" s="15" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Taux de change CHF/USD et CHF/EUR</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Taux de change de référence</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>Banque nationale suisse</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>https://data.snb.ch</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="n">
+        <v>4308</v>
+      </c>
+      <c r="P47" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q47" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Commerce mondial de marchandises (volume)</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>World Trade Monitor</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="N48" s="11" t="inlineStr">
+        <is>
+          <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
+        </is>
+      </c>
+      <c r="O48" s="11" t="n">
+        <v>287</v>
+      </c>
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-05</t>
+        </is>
+      </c>
+      <c r="Q48" s="11" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Croissance du PIB mondial</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>World Economic Outlook</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Fonds monétaire international</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>pourcentage</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>https://www.imf.org/en/Publications/WEO</t>
+        </is>
+      </c>
+      <c r="O49" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="P49" s="11" t="inlineStr">
+        <is>
+          <t>2014 → 2025</t>
+        </is>
+      </c>
+      <c r="Q49" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Attentes de production de l'industrie européenne (solde d'opinion à 3 mois)</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>Commission européenne</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>solde d'opinion</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>API + CSV</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="n">
+        <v>3192</v>
+      </c>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q50" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Socle transversal</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Baromètre conjoncturel KOF (Suisse)</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>QV0</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Baromètre conjoncturel KOF</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>KOF ETH Zurich</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>certifie</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>API / CSV</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr">
+        <is>
+          <t>https://data.kof.ethz.ch</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="n">
+        <v>1167</v>
+      </c>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2023-01 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q51" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Production de l'usinage et du traitement des métaux UE (NACE C25.6)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>QV0</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Commission européenne</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>indice</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K44" s="11" t="n"/>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="K52" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="M52" s="11" t="inlineStr">
         <is>
           <t>API + CSV</t>
         </is>
       </c>
-      <c r="N44" s="11" t="inlineStr">
+      <c r="N52" s="11" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
-      <c r="O44" s="11" t="n">
-        <v>1902</v>
-      </c>
-      <c r="P44" s="11" t="inlineStr">
+      <c r="O52" s="11" t="n">
+        <v>3102</v>
+      </c>
+      <c r="P52" s="11" t="inlineStr">
         <is>
           <t>2014-01 → 2026-06</t>
         </is>
       </c>
-      <c r="Q44" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="Q52" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>État du carnet de commandes de l'industrie UE (enquête de conjoncture)</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>QV0</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Commission européenne</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>solde</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K45" s="11" t="n"/>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M53" s="11" t="inlineStr">
         <is>
           <t>API + CSV</t>
         </is>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N53" s="11" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
-      <c r="O45" s="11" t="n">
-        <v>1704</v>
-      </c>
-      <c r="P45" s="11" t="inlineStr">
-        <is>
-          <t>2014-01 → 2026-07</t>
-        </is>
-      </c>
-      <c r="Q45" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="O53" s="11" t="n">
+        <v>2918</v>
+      </c>
+      <c r="P53" s="11" t="inlineStr">
+        <is>
+          <t>2014-01 → 2026-08</t>
+        </is>
+      </c>
+      <c r="Q53" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>T9</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Socle transversal</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Taux d'utilisation des capacités de l'industrie UE</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>QV0</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Commission européenne</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>trimestrielle</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>pourcentage</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr">
         <is>
           <t>certifie</t>
         </is>
       </c>
-      <c r="K46" s="11" t="n"/>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="K54" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="M46" s="11" t="inlineStr">
+      <c r="M54" s="11" t="inlineStr">
         <is>
           <t>API + CSV</t>
         </is>
       </c>
-      <c r="N46" s="11" t="inlineStr">
+      <c r="N54" s="11" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
-      <c r="O46" s="11" t="n">
-        <v>561</v>
-      </c>
-      <c r="P46" s="11" t="inlineStr">
+      <c r="O54" s="11" t="n">
+        <v>969</v>
+      </c>
+      <c r="P54" s="11" t="inlineStr">
         <is>
           <t>2014-T1 → 2026-T3</t>
         </is>
       </c>
-      <c r="Q46" s="11" t="n">
-        <v>150</v>
+      <c r="Q54" s="11" t="n">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q46"/>
+  <autoFilter ref="A1:Q54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5018,7 +5656,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Quelles ruptures techniques — lanceurs réutilisables, constellations, propulsion alternative — modifient les volumes et les tolérances demandés ?</t>
+          <t>Quelles ruptures techniques, lanceurs réutilisables, constellations, propulsion alternative, modifient les volumes et les tolérances demandés ?</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -5032,7 +5670,7 @@
         </is>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>0</v>
@@ -5137,7 +5775,7 @@
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Les immatriculations mesurent la demande finale, le commerce de pièces mesure le marché directement adressable par la sous-traitance. Les deux peuvent diverger — un marché stable en véhicules peut se contracter en pièces si le contenu mécanique par véhicule diminue.</t>
+          <t>Les immatriculations mesurent la demande finale, le commerce de pièces mesure le marché directement adressable par la sous-traitance. Les deux peuvent diverger : un marché stable en véhicules peut se contracter en pièces si le contenu mécanique par véhicule diminue.</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -5146,7 +5784,7 @@
         </is>
       </c>
       <c r="G8" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>4</v>
@@ -5222,10 +5860,10 @@
         </is>
       </c>
       <c r="G10" s="16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5246,12 +5884,12 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Quelles décisions réglementaires — normes d'émission, calendrier d'interdiction du thermique, dispositifs d'incitation — modifient la composition de la demande ?</t>
+          <t>Quelles décisions réglementaires, normes d'émission, calendrier d'interdiction du thermique, dispositifs d'incitation, modifient la composition de la demande ?</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>L'action publique ne finance ni n'achète : elle fixe le calendrier de la substitution technologique. Elle agit sur la composition de la demande, non sur son niveau — ce qui explique qu'aucune série statistique budgétaire ne la capte.</t>
+          <t>L'action publique ne finance ni n'achète : elle fixe le calendrier de la substitution technologique. Elle agit sur la composition de la demande, non sur son niveau : ce qui explique qu'aucune série statistique budgétaire ne la capte.</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -5260,7 +5898,7 @@
         </is>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>0</v>
@@ -5298,10 +5936,10 @@
         </is>
       </c>
       <c r="G12" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="16" t="n">
         <v>5</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -5412,47 +6050,47 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Horlogerie</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>QV5</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Impulsions publiques</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Quelles décisions publiques — droits de douane, accords commerciaux, réglementation Swiss made — modifient les conditions d'accès aux marchés ?</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Quelles décisions publiques, droits de douane, accords commerciaux, réglementation Swiss made, modifient les conditions d'accès aux marchés ?</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>L'action publique n'est ici ni acheteuse ni finançante : elle agit sur les conditions d'accès et les règles d'origine, donc sur les prix relatifs et non sur le niveau de la demande. Le choc douanier de 2025 constitue l'exception qui rend la question observable.</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>marginale</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="n">
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>significative</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5588,7 +6226,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Quelles mutations techniques — chirurgie mini-invasive, robotique, implants personnalisés — recomposent la demande de pièces de précision ?</t>
+          <t>Quelles mutations techniques, chirurgie mini-invasive, robotique, implants personnalisés, recomposent la demande de pièces de précision ?</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
@@ -5781,7 +6419,7 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -5806,7 +6444,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -5856,7 +6494,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -5872,7 +6510,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Quelle action publique — dépense, réglementation, condition d'accès — modifie le niveau ou la composition de la demande à moyen terme ?</t>
+          <t>Quelle action publique : dépense, réglementation, condition d'accès : modifie le niveau ou la composition de la demande à moyen terme ?</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -5881,7 +6519,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6004,25 +6642,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>aerospatial</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>non couverte</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>couverte a confirmer</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6722,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>4</v>
@@ -6130,37 +6768,37 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>couverte</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>automobile</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>QV5</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>couverte</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>automobile</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>QV5</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
+      <c r="D11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>non couverte</t>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>couverte a confirmer</t>
         </is>
       </c>
     </row>
@@ -6176,10 +6814,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>4</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -6245,7 +6883,7 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>1</v>
@@ -6437,7 +7075,7 @@
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
@@ -6486,78 +7124,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Aérospatial</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>QV4</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Dynamique technologique</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Quelles ruptures techniques — lanceurs réutilisables, constellations, propulsion alternative — modifient les volumes et les tolérances demandés ?</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Quelles ruptures techniques, lanceurs réutilisables, constellations, propulsion alternative, modifient les volumes et les tolérances demandés ?</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>dominante</t>
         </is>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>couverture nominale — aucun indicateur certifié</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Automobile</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>QV5</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Impulsions publiques</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Quelles décisions réglementaires, normes d'émission, calendrier d'interdiction du thermique, dispositifs d'incitation, modifient la composition de la demande ?</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>dominante</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="15" t="inlineStr">
-        <is>
-          <t>lacune — aucun indicateur</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Automobile</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>QV5</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>Impulsions publiques</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>Quelles décisions réglementaires — normes d'émission, calendrier d'interdiction du thermique, dispositifs d'incitation — modifient la composition de la demande ?</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>dominante</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
-          <t>lacune — aucun indicateur</t>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>couverture nominale — aucun indicateur certifié</t>
         </is>
       </c>
     </row>
@@ -6579,12 +7217,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Quelles décisions publiques — droits de douane, accords commerciaux, réglementation Swiss made — modifient les conditions d'accès aux marchés ?</t>
+          <t>Quelles décisions publiques, droits de douane, accords commerciaux, réglementation Swiss made, modifient les conditions d'accès aux marchés ?</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>marginale</t>
+          <t>significative</t>
         </is>
       </c>
       <c r="F4" s="13" t="n">
@@ -6612,17 +7250,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
@@ -6801,7 +7439,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A11, A3</t>
         </is>
       </c>
       <c r="K3" s="11" t="inlineStr">
@@ -6931,7 +7569,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade — commerce international par code SH</t>
+          <t>UN Comtrade : commerce international par code SH</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -7050,265 +7688,265 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
+          <t>cp</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Recensement du personnel et des entreprises des industries horlogère et microtechnique suisses</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Convention patronale de l'industrie horlogère suisse</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>PDF (lecture multimodale)</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>H11, H2</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>https://cpih.ch/statistiques/</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>Association patronale, PAS une statistique publique — provenance à déclarer comme pour la FH (§ 8.6.4) ; ne jamais étiqueter « donnée officielle ». Recensement au 30 septembre, publication en décembre. La page d'index est STABLE, le nom du PDF change chaque année : le lien se résout depuis l'index, comme pour la FH et le classeur SIPRI. Tableau Tb. 1e = série 2005-2025, effectifs et entreprises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
           <t>cpb</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>World Trade Monitor</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>URL corrigée le 24.08.2026 : l'ancienne (…/en/worldtrademonitor) renvoyait 404. La nouvelle redirige vers le millésime courant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>deloitte</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Watch Industry Study</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>https://www.deloitte.com/ch</t>
-        </is>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>Étude annuelle, méthodologie déclarative</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
+          <t>deloitte</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Watch Industry Study</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/ch</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>Étude annuelle, méthodologie déclarative</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
           <t>esa</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Budgets spatiaux publics</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>ESA et agences nationales</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>https://www.esa.int</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>Formats hétérogènes selon les agences</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>eurostat</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat — statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Commission européenne</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>A5, A6, H6, M2, S8, T10, T11, T5, T7, T8, T9</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>API de dissémination sans authentification</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>fh</t>
+          <t>eurostat</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Statistiques d'exportation horlogère</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Fédération de l'industrie horlogère suisse</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -7318,7 +7956,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -7338,221 +7976,221 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>09.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>H7, H8, H9</t>
+          <t>A5, A6, H6, M2, S8, T10, T11, T5, T7, T8, T9</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>https://www.fhs.swiss</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>Détail par marché de destination</t>
+          <t>API de dissémination sans authentification</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>fh</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Statistiques d'exportation horlogère</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Fédération de l'industrie horlogère suisse</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>PDF / communiqués</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>09.08.2026</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>H7, H8, H9</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fhs.swiss</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>Détail par marché de destination. Provenance précisée le 27.08.2026 : la FH rediffuse la statistique douanière suisse du commerce extérieur (OFDF) en y ajoutant le détail de branche (mécanique/quartz, destinations) — source secondaire d'un chiffre officiel, qualifiée comme référence de branche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>fmi</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>World Economic Outlook</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Fonds monétaire international</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>semestrielle</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>https://www.imf.org/en/Publications/WEO</t>
         </is>
       </c>
-      <c r="L13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="L14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>iata</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Air Passenger Market Analysis</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>IATA</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>https://www.iata.org</t>
         </is>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>Séries détaillées réservées aux membres</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>kof</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Baromètre conjoncturel KOF</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>KOF ETH Zurich</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>API / CSV</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>https://data.kof.ethz.ch</t>
-        </is>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>API v2 publique sans clé (access_type=public), CSV date/valeur, mensuel depuis 1991. Vérifiée en réponse réelle le 17.08.2026. Ancienne API v1 hors service — motif du re-sourçage documenté.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>ocde</t>
+          <t>kof</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>Baromètre conjoncturel KOF</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>KOF ETH Zurich</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -7562,7 +8200,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -7582,34 +8220,34 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
+          <t>https://data.kof.ethz.ch</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>Vérifié le 10.08.2026 : la série CLI est vivante et mensuelle, mais l'agrégat « OCDE total » n'est plus publié — 22 zones disponibles dont G20, G7, G4E, NAFTA. T1 réancré sur G20. Version du flux non épinglée : la 4.1 ne porte plus la mesure LI. Limitation de débit annoncée par la documentation sans être chiffrée.</t>
+          <t>API v2 publique sans clé (access_type=public), CSV date/valeur, mensuel depuis 1991. Vérifiée en réponse réelle le 17.08.2026. Ancienne API v1 hors service — motif du re-sourçage documenté.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>ocde_brevets</t>
+          <t>ocde</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Brevets par domaine technologique</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -7619,12 +8257,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>API SDMX</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -7644,39 +8282,39 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>A7, M6</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>Jeu DF_PATENTS_OECDSPECIFIC. Dix-huit domaines technologiques, dont MEDICAL et TRA (technologies de transport bas carbone). Sans clé. Vérifié en réponse réelle le 25.08.2026 : 13 points annuels 2010-2022, 106 zones disponibles.</t>
+          <t>Vérifié le 10.08.2026 : la série CLI est vivante et mensuelle, mais l'agrégat « OCDE total » n'est plus publié — 22 zones disponibles dont G20, G7, G4E, NAFTA. T1 réancré sur G20. Version du flux non épinglée : la 4.1 ne porte plus la mesure LI. Limitation de débit annoncée par la documentation sans être chiffrée.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>ofs</t>
+          <t>ocde_brevets</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>STATENT et statistiques conjoncturelles</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -7686,7 +8324,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>CSV / Excel</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -7706,39 +8344,39 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>H2, M4</t>
+          <t>A7, M6</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>https://www.bfs.admin.ch</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>Nomenclature NOGA</t>
+          <t>Jeu DF_PATENTS_OECDSPECIFIC. Dix-huit domaines technologiques, dont MEDICAL et TRA (technologies de transport bas carbone). Sans clé. Vérifié en réponse réelle le 25.08.2026 : 13 points annuels 2010-2022, 106 zones disponibles.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>oica</t>
+          <t>ofs</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>STATENT : Etablissements et emplois selon année, canton, genre économique et unité d'observation (table px-x-0602010000_103)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>OICA</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -7748,7 +8386,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>API PX-Web (JSON-stat2, requête POST)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -7768,35 +8406,39 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H12, M4</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="n"/>
+          <t>https://www.pxweb.bfs.admin.ch/api/v1/fr/px-x-0602010000_103/px-x-0602010000_103.px</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>Nomenclature NOGA. Cube STATENT interrogé en POST : le seul URL ne rend pas la donnée, le corps de requête fait partie de la référence (voir source_bindings 142 et 143). H2 = cinq classes NOGA 2652 sommées ; M4 = NOGA 266000 et 3250xx. Unité d'observation 2 (emplois) ; la modalité 1 (établissements) est identifiée, non instrumentée. Consultation à l'écran de la même table : https://www.pxweb.bfs.admin.ch/pxweb/fr/px-x-0602010000_103/px-x-0602010000_103/px-x-0602010000_103.px</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>ompi</t>
+          <t>oica</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>Statistiques de production automobile</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -7806,7 +8448,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>Tableaux web</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -7831,29 +8473,25 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ipstats</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>Classification CIB</t>
-        </is>
-      </c>
+          <t>https://www.oica.net/production-statistics</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>ompi_tech</t>
+          <t>ompi</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Indicateurs de brevets par domaine technologique</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -7868,7 +8506,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>ZIP / CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -7888,39 +8526,39 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>T12, T13</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/ip-statistics</t>
+          <t>https://www.wipo.int/ipstats</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>Archive wipo-data-patent-indicators.zip, téléchargement direct sans inscription. Comptages par année, office, pays d'origine et domaine technologique (35 domaines). Vérifié en réponse réelle le 25.08.2026 : 663 584 lignes, 2000-2022. Table de concordance CIB/domaine publiée séparément et consultée pour établir les limites de granularité — G04 tombe dans « Techniques de mesure », B64 dans « Transport ».</t>
+          <t>Classification CIB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>oms_ghed</t>
+          <t>ompi_tech</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -7930,7 +8568,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>ZIP / CSV</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -7950,45 +8588,49 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>T12, T13</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="n"/>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>Archive wipo-data-patent-indicators.zip, téléchargement direct sans inscription. Comptages par année, office, pays d'origine et domaine technologique (35 domaines). Vérifié en réponse réelle le 25.08.2026 : 663 584 lignes, 2000-2022. Table de concordance CIB/domaine publiée séparément et consultée pour établir les limites de granularité — G04 tombe dans « Techniques de mesure », B64 dans « Transport ».</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>openfda</t>
+          <t>oms_ghed</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>openFDA — bases publiques de la Food and Drug Administration</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>U.S. Food and Drug Administration</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>quotidienne</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -8008,142 +8650,142 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>https://open.fda.gov</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
-        </is>
-      </c>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
+          <t>openfda</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>openFDA : bases publiques de la Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>U.S. Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>https://open.fda.gov</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>sipri</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Military Expenditure Database</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>SIPRI</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>https://www.sipri.org/databases/milex</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L25" s="11" t="inlineStr">
         <is>
           <t>URL corrigée le 24.08.2026 : l'ancienne (milex.sipri.org) échouait à la négociation TLS. Adresse alignée sur celle de la liaison S4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>sp_global_pmi</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Indices PMI manufacturiers</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Communiqués</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>payant</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>https://www.pmi.spglobal.com</t>
-        </is>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>Indices détaillés payants ; valeurs de synthèse dans les communiqués</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8859,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Tenders Electronic Daily — marchés publics UE</t>
+          <t>Tenders Electronic Daily : marchés publics UE</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -8257,7 +8899,7 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>M7, S7</t>
+          <t>A8, M7, S7</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
@@ -8272,65 +8914,127 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>triage_flux</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Intensité de signalement dans les flux qualifiés (dérivation interne)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispositif de veille : dérivation du triage IA (v_intensite_signalement)</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>N. Castillo (délégation du 27.08.2026)</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>A10, A9, H10, S9</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>interne : flux_sources → flux_items → flux_triage_ia → v_intensite_signalement</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>Non pas une source externe mais une dérivation : part mensuelle des items triés attribués à une question de veille. Hérite de la qualification des flux sous-jacents (tous en accès libre). a_confirmer tant que le corpus est jeune (démarré fin 07.2026) et sa composition mouvante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>unoosa</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Objets lancés dans l'espace</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>UNOOSA / Our World in Data</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>https://ourworldindata.org/space-exploration-satellites</t>
         </is>
       </c>
-      <c r="L28" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/exports/1_tableau_de_veille.xlsx
+++ b/exports/1_tableau_de_veille.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Couverture QV'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lacunes'!$A$1:$H$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lacunes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources'!$A$1:$L$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Sources'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02.09.2026 à 07:55</t>
+          <t>04.09.2026 à 18:33</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>Production mondiale de véhicules par pays — tableau republié dans l'annuaire du CCFA « L'industrie automobile française » (mention imprimée « Source : OICA »), document collecté ; classements top-10 de la page OICA en vérité terrain</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>PDF (annuaire CCFA, https://ccfa.fr/analyses-et-statistiques/) ; tableaux web OICA pour la confrontation opportuniste</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
@@ -7250,10 +7250,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -7392,77 +7392,77 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>aie</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Global EV Data Explorer</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Agence internationale de l'énergie</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>acea_incitations</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Electric cars: tax benefits and incentives (fiscalité et aides à l'achat, par pays)</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>ACEA</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>PDF tabulaire (tableau comparatif par pays)</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>A11, A3</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>https://www.iea.org</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="n"/>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.acea.auto/fact/electric-cars-tax-benefits-and-incentives-2025/</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>Issue de la couche 0 (run du 22.08.2026, QV5 automobile, candidat 2, 3 modèles sur 4). Inscrite le 02.09.2026 sans liaison de collecte : accès vérifié en réponse réelle (HTTP 200 les 22.08 et 02.09), granularité d'extraction non validée. Pas d'indicateur rattaché à ce jour.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>banque_mondiale</t>
+          <t>aie</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Séries macroéconomiques mondiales</t>
+          <t>Global EV Data Explorer</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Banque mondiale</t>
+          <t>Agence internationale de l'énergie</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -7495,10 +7495,14 @@
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J4" s="11" t="n"/>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>A11, A3</t>
+        </is>
+      </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>https://data.worldbank.org</t>
+          <t>https://www.iea.org</t>
         </is>
       </c>
       <c r="L4" s="11" t="n"/>
@@ -7506,27 +7510,27 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>bns</t>
+          <t>banque_mondiale</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Taux de change de référence</t>
+          <t>Séries macroéconomiques mondiales</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Banque nationale suisse</t>
+          <t>Banque mondiale</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -7549,14 +7553,10 @@
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>https://data.snb.ch</t>
+          <t>https://data.worldbank.org</t>
         </is>
       </c>
       <c r="L5" s="11" t="n"/>
@@ -7564,32 +7564,32 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>comtrade</t>
+          <t>bns</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>UN Comtrade : commerce international par code SH</t>
+          <t>Taux de change de référence</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Nations Unies</t>
+          <t>Banque nationale suisse</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>libre_quota</t>
+          <t>libre</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -7609,49 +7609,45 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>A4, H1, H3, M1, S6</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>Quota sur l'API publique</t>
-        </is>
-      </c>
+          <t>https://data.snb.ch</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>constructeurs</t>
+          <t>comtrade</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Commandes et livraisons d'avions commerciaux</t>
+          <t>UN Comtrade : commerce international par code SH</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Airbus, Boeing</t>
+          <t>Nations Unies</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>mensuelle</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Web / Excel</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>libre</t>
+          <t>libre_quota</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -7671,44 +7667,44 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>A4, H1, H3, M1, S6</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>https://www.airbus.com</t>
+          <t>https://comtradeplus.un.org</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>Deux producteurs à consolider</t>
+          <t>Quota sur l'API publique</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>cp</t>
+          <t>constructeurs</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Recensement du personnel et des entreprises des industries horlogère et microtechnique suisses</t>
+          <t>Commandes et livraisons d'avions commerciaux</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Convention patronale de l'industrie horlogère suisse</t>
+          <t>Airbus, Boeing</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>PDF (lecture multimodale)</t>
+          <t>Web / Excel</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -7728,287 +7724,287 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>H11, H2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>https://cpih.ch/statistiques/</t>
+          <t>https://www.airbus.com</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>Association patronale, PAS une statistique publique — provenance à déclarer comme pour la FH (§ 8.6.4) ; ne jamais étiqueter « donnée officielle ». Recensement au 30 septembre, publication en décembre. La page d'index est STABLE, le nom du PDF change chaque année : le lien se résout depuis l'index, comme pour la FH et le classeur SIPRI. Tableau Tb. 1e = série 2005-2025, effectifs et entreprises.</t>
+          <t>Deux producteurs à consolider</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
+          <t>cp</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Recensement du personnel et des entreprises des industries horlogère et microtechnique suisses</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Convention patronale de l'industrie horlogère suisse</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>PDF (lecture multimodale)</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>H11, H2</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>https://cpih.ch/statistiques/</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>Association patronale, PAS une statistique publique — provenance à déclarer comme pour la FH (§ 8.6.4) ; ne jamais étiqueter « donnée officielle ». Recensement au 30 septembre, publication en décembre. La page d'index est STABLE, le nom du PDF change chaque année : le lien se résout depuis l'index, comme pour la FH et le classeur SIPRI. Tableau Tb. 1e = série 2005-2025, effectifs et entreprises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
           <t>cpb</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>World Trade Monitor</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>CPB Netherlands Bureau for Economic Policy Analysis</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>https://www.cpb.nl/en/worldtrademonitor/latest</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>URL corrigée le 24.08.2026 : l'ancienne (…/en/worldtrademonitor) renvoyait 404. La nouvelle redirige vers le millésime courant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>deloitte</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Swiss Watch Industry Study</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>annuelle</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>a_confirmer</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>https://www.deloitte.com/ch</t>
-        </is>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>Étude annuelle, méthodologie déclarative</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
+          <t>deloitte</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Swiss Watch Industry Study</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>annuelle</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/ch</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>Étude annuelle, méthodologie déclarative</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
           <t>esa</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Budgets spatiaux publics</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>ESA et agences nationales</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>https://www.esa.int</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>Formats hétérogènes selon les agences</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>eurostat</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Commission européenne</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>API + CSV</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>A5, A6, H6, M2, S8, T10, T11, T5, T7, T8, T9</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/data/database</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>API de dissémination sans authentification</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>fh</t>
+          <t>eurostat</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Statistiques d'exportation horlogère</t>
+          <t>Eurostat : statistiques conjoncturelles et structurelles</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Fédération de l'industrie horlogère suisse</t>
+          <t>Commission européenne</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -8018,7 +8014,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>PDF / communiqués</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -8038,221 +8034,221 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>09.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>H7, H8, H9</t>
+          <t>A5, A6, H6, M2, S8, T10, T11, T5, T7, T8, T9</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>https://www.fhs.swiss</t>
+          <t>https://ec.europa.eu/eurostat/data/database</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>Détail par marché de destination. Provenance précisée le 27.08.2026 : la FH rediffuse la statistique douanière suisse du commerce extérieur (OFDF) en y ajoutant le détail de branche (mécanique/quartz, destinations) — source secondaire d'un chiffre officiel, qualifiée comme référence de branche.</t>
+          <t>API de dissémination sans authentification</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
+          <t>fh</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Statistiques d'exportation horlogère</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Fédération de l'industrie horlogère suisse</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>mensuelle</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PDF / communiqués</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>09.08.2026</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>H7, H8, H9</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fhs.swiss</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Détail par marché de destination. Provenance précisée le 27.08.2026 : la FH rediffuse la statistique douanière suisse du commerce extérieur (OFDF) en y ajoutant le détail de branche (mécanique/quartz, destinations) — source secondaire d'un chiffre officiel, qualifiée comme référence de branche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
           <t>fmi</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>World Economic Outlook</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Fonds monétaire international</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>semestrielle</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>https://www.imf.org/en/Publications/WEO</t>
         </is>
       </c>
-      <c r="L14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="L15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>iata</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Air Passenger Market Analysis</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>IATA</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J15" s="13" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>https://www.iata.org</t>
         </is>
       </c>
-      <c r="L15" s="13" t="inlineStr">
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>Séries détaillées réservées aux membres</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>kof</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Baromètre conjoncturel KOF</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>KOF ETH Zurich</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>mensuelle</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>API / CSV</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>libre</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>certifiee</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>N. Castillo</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>https://data.kof.ethz.ch</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>API v2 publique sans clé (access_type=public), CSV date/valeur, mensuel depuis 1991. Vérifiée en réponse réelle le 17.08.2026. Ancienne API v1 hors service — motif du re-sourçage documenté.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>ocde</t>
+          <t>kof</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Principaux indicateurs économiques et CLI</t>
+          <t>Baromètre conjoncturel KOF</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>OCDE</t>
+          <t>KOF ETH Zurich</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -8262,7 +8258,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>API + CSV</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -8282,34 +8278,34 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org</t>
+          <t>https://data.kof.ethz.ch</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>Vérifié le 10.08.2026 : la série CLI est vivante et mensuelle, mais l'agrégat « OCDE total » n'est plus publié — 22 zones disponibles dont G20, G7, G4E, NAFTA. T1 réancré sur G20. Version du flux non épinglée : la 4.1 ne porte plus la mesure LI. Limitation de débit annoncée par la documentation sans être chiffrée.</t>
+          <t>API v2 publique sans clé (access_type=public), CSV date/valeur, mensuel depuis 1991. Vérifiée en réponse réelle le 17.08.2026. Ancienne API v1 hors service — motif du re-sourçage documenté.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>ocde_brevets</t>
+          <t>ocde</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Brevets par domaine technologique</t>
+          <t>Principaux indicateurs économiques et CLI</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -8319,12 +8315,12 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>annuelle</t>
+          <t>mensuelle</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>API SDMX</t>
+          <t>API + CSV</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -8344,39 +8340,39 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>A7, M6</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
+          <t>https://data-explorer.oecd.org</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>Jeu DF_PATENTS_OECDSPECIFIC. Dix-huit domaines technologiques, dont MEDICAL et TRA (technologies de transport bas carbone). Sans clé. Vérifié en réponse réelle le 25.08.2026 : 13 points annuels 2010-2022, 106 zones disponibles.</t>
+          <t>Vérifié le 10.08.2026 : la série CLI est vivante et mensuelle, mais l'agrégat « OCDE total » n'est plus publié — 22 zones disponibles dont G20, G7, G4E, NAFTA. T1 réancré sur G20. Version du flux non épinglée : la 4.1 ne porte plus la mesure LI. Limitation de débit annoncée par la documentation sans être chiffrée.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>ofs</t>
+          <t>ocde_brevets</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>STATENT : Etablissements et emplois selon année, canton, genre économique et unité d'observation (table px-x-0602010000_103)</t>
+          <t>Brevets par domaine technologique</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Office fédéral de la statistique</t>
+          <t>OCDE</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -8386,7 +8382,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>API PX-Web (JSON-stat2, requête POST)</t>
+          <t>API SDMX</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -8406,39 +8402,39 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>H12, M4</t>
+          <t>A7, M6</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>https://www.pxweb.bfs.admin.ch/api/v1/fr/px-x-0602010000_103/px-x-0602010000_103.px</t>
+          <t>https://data-explorer.oecd.org/vis?df[ag]=OECD.STI.PIE&amp;df[id]=DSD_PATENTS@DF_PATENTS_OECDSPECIFIC</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>Nomenclature NOGA. Cube STATENT interrogé en POST : le seul URL ne rend pas la donnée, le corps de requête fait partie de la référence (voir source_bindings 142 et 143). H2 = cinq classes NOGA 2652 sommées ; M4 = NOGA 266000 et 3250xx. Unité d'observation 2 (emplois) ; la modalité 1 (établissements) est identifiée, non instrumentée. Consultation à l'écran de la même table : https://www.pxweb.bfs.admin.ch/pxweb/fr/px-x-0602010000_103/px-x-0602010000_103/px-x-0602010000_103.px</t>
+          <t>Jeu DF_PATENTS_OECDSPECIFIC. Dix-huit domaines technologiques, dont MEDICAL et TRA (technologies de transport bas carbone). Sans clé. Vérifié en réponse réelle le 25.08.2026 : 13 points annuels 2010-2022, 106 zones disponibles.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>oica</t>
+          <t>ofs</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de production automobile</t>
+          <t>STATENT : Etablissements et emplois selon année, canton, genre économique et unité d'observation (table px-x-0602010000_103)</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>OICA</t>
+          <t>Office fédéral de la statistique</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -8448,7 +8444,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Tableaux web</t>
+          <t>API PX-Web (JSON-stat2, requête POST)</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -8468,35 +8464,39 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H12, M4</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>https://www.oica.net/production-statistics</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="n"/>
+          <t>https://www.pxweb.bfs.admin.ch/api/v1/fr/px-x-0602010000_103/px-x-0602010000_103.px</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>Nomenclature NOGA. Cube STATENT interrogé en POST : le seul URL ne rend pas la donnée, le corps de requête fait partie de la référence (voir source_bindings 142 et 143). H2 = cinq classes NOGA 2652 sommées ; M4 = NOGA 266000 et 3250xx. Unité d'observation 2 (emplois) ; la modalité 1 (établissements) est identifiée, non instrumentée. Consultation à l'écran de la même table : https://www.pxweb.bfs.admin.ch/pxweb/fr/px-x-0602010000_103/px-x-0602010000_103/px-x-0602010000_103.px</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>ompi</t>
+          <t>oica</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Statistiques de propriété intellectuelle</t>
+          <t>Production mondiale de véhicules par pays — tableau republié dans l'annuaire du CCFA « L'industrie automobile française » (mention imprimée « Source : OICA »), document collecté ; classements top-10 de la page OICA en vérité terrain</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>OMPI</t>
+          <t>OICA</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>PDF (annuaire CCFA, https://ccfa.fr/analyses-et-statistiques/) ; tableaux web OICA pour la confrontation opportuniste</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -8526,34 +8526,34 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/ipstats</t>
+          <t>https://www.oica.net/production-statistics</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>Classification CIB</t>
+          <t>Producteur : OICA. Document collecté : annuaire CCFA (association professionnelle française), PDF, une édition par an, tableau « La production mondiale de véhicules » par pays en milliers, mention « Source : OICA » imprimée. Éditions traitées au 31.08.2026 : page des analyses et statistiques (édition courante), CCFA-2023, CCFA-2024 (composite_queue 9-11), série 2021-2024. Découpe par sentinelles avant envoi aux modèles (~1 % du document : 5 100 caractères sur ~530 000, mesuré sur les exécutions du 31.08.2026 ; corrigé de 2,5 % le 04.09). Vérité terrain de rang 1 : classements top-10 de https://www.oica.net/production-statistics, JSON incorporé, confrontation opportuniste (non_verifiable quand l'année n'est pas servie, jamais de faux verdict). Détection des nouvelles éditions : workflow veille_documentaire_annuelle.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>ompi_tech</t>
+          <t>ompi</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Indicateurs de brevets par domaine technologique</t>
+          <t>Statistiques de propriété intellectuelle</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>ZIP / CSV</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -8588,39 +8588,39 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>T12, T13</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>https://www.wipo.int/en/web/ip-statistics</t>
+          <t>https://www.wipo.int/ipstats</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>Archive wipo-data-patent-indicators.zip, téléchargement direct sans inscription. Comptages par année, office, pays d'origine et domaine technologique (35 domaines). Vérifié en réponse réelle le 25.08.2026 : 663 584 lignes, 2000-2022. Table de concordance CIB/domaine publiée séparément et consultée pour établir les limites de granularité — G04 tombe dans « Techniques de mesure », B64 dans « Transport ».</t>
+          <t>Classification CIB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>oms_ghed</t>
+          <t>ompi_tech</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Global Health Expenditure Database</t>
+          <t>Indicateurs de brevets par domaine technologique</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OMPI</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>API / CSV</t>
+          <t>ZIP / CSV</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -8650,45 +8650,49 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>T12, T13</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>https://apps.who.int/nha/database</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="n"/>
+          <t>https://www.wipo.int/en/web/ip-statistics</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>Archive wipo-data-patent-indicators.zip, téléchargement direct sans inscription. Comptages par année, office, pays d'origine et domaine technologique (35 domaines). Vérifié en réponse réelle le 25.08.2026 : 663 584 lignes, 2000-2022. Table de concordance CIB/domaine publiée séparément et consultée pour établir les limites de granularité — G04 tombe dans « Techniques de mesure », B64 dans « Transport ».</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>openfda</t>
+          <t>oms_ghed</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>openFDA : bases publiques de la Food and Drug Administration</t>
+          <t>Global Health Expenditure Database</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>U.S. Food and Drug Administration</t>
+          <t>OMS</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>quotidienne</t>
+          <t>annuelle</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>API / CSV</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -8708,333 +8712,391 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>https://open.fda.gov</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
-        </is>
-      </c>
+          <t>https://apps.who.int/nha/database</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
+          <t>openfda</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>openFDA : bases publiques de la Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>U.S. Food and Drug Administration</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>quotidienne</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>libre</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>certifiee</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>N. Castillo</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>https://open.fda.gov</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>API libre et sans clé (quota anonyme). Vérifiée en réponse réelle le 23.08.2026 : onze mois consécutifs de décomptes 510(k). Deux pièges d'appel consignés — la syntaxe d'intervalle « champ:[debut+TO+fin] » ne doit pas voir son « + » encodé (sinon 500), et une recherche sans résultat répond 404 et non 200 avec liste vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>sipri</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Military Expenditure Database</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>SIPRI</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>https://www.sipri.org/databases/milex</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>URL corrigée le 24.08.2026 : l'ancienne (milex.sipri.org) échouait à la négociation TLS. Adresse alignée sur celle de la liaison S4.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>swiss_medtech</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Swiss Medical Technology Industry report</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Swiss Medtech</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>bisannuelle</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>https://www.swiss-medtech.ch</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="L27" s="13" t="inlineStr">
         <is>
           <t>Publication bisannuelle, périodes non alignées sur la fenêtre 2023-2025</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>ted</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Tenders Electronic Daily : marchés publics UE</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Office des publications de l'UE</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>quotidienne</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>20.08.2026</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>A8, M7, S7</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>https://ted.europa.eu</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L28" s="11" t="inlineStr">
         <is>
           <t>API de recherche v3, POST JSON, sans clé pour la recherche. Vérifiée en réponse réelle le 20.08.2026 (totalNoticeCount par requête CPV + bornes de dates). Source de la famille OSINT F3 (marchés publics) de la demande de ratification.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>triage_flux</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Intensité de signalement dans les flux qualifiés (dérivation interne)</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Dispositif de veille : dérivation du triage IA (v_intensite_signalement)</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>mensuelle</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>sql</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>a_confirmer</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>N. Castillo (délégation du 27.08.2026)</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>27.08.2026</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>A10, A9, H10, S9</t>
         </is>
       </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>interne : flux_sources → flux_items → flux_triage_ia → v_intensite_signalement</t>
         </is>
       </c>
-      <c r="L28" s="13" t="inlineStr">
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>Non pas une source externe mais une dérivation : part mensuelle des items triés attribués à une question de veille. Hérite de la qualification des flux sous-jacents (tous en accès libre). a_confirmer tant que le corpus est jeune (démarré fin 07.2026) et sa composition mouvante.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>unoosa</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Objets lancés dans l'espace</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>UNOOSA / Our World in Data</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>annuelle</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>libre</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>certifiee</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>N. Castillo</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>https://ourworldindata.org/space-exploration-satellites</t>
         </is>
       </c>
-      <c r="L29" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:L30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
